--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-65.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-486.7%</t>
+          <t>-486.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-131.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-132.3%</t>
+          <t>-125.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-21.4%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.35226027298226</v>
+        <v>-3.280402348419501</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.201661853291636</v>
+        <v>1.23040502311674</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.856039512139671</v>
+        <v>2.899154266877326</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.292407653778537</v>
+        <v>-3.220549729215778</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.235775287405258</v>
+        <v>1.264518457230362</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.866211898571803</v>
+        <v>2.909326653309459</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.206164190752159</v>
+        <v>-3.1343062661894</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.265218943189669</v>
+        <v>1.293962113014773</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.861158169145663</v>
+        <v>2.904272923883319</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.251471010151139</v>
+        <v>-3.17961308558838</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.238871990874603</v>
+        <v>1.267615160699707</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.481051712559741</v>
+        <v>0.5529096371225</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.828447846784651</v>
+        <v>2.871562601522306</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.280504114853441</v>
+        <v>-3.208646190290681</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.227810622026784</v>
+        <v>1.256553791851887</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.481051712559741</v>
+        <v>0.5529096371225</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.828999719817752</v>
+        <v>2.872114474555408</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.187693633402581</v>
+        <v>-3.115835708839822</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.194207506498493</v>
+        <v>1.222950676323597</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5738621940106003</v>
+        <v>0.6457201185733593</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.813958700579633</v>
+        <v>2.857073455317289</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.232083102732009</v>
+        <v>-3.16022517816925</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.178325194691323</v>
+        <v>1.207068364516427</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5294727246811727</v>
+        <v>0.6013306492439316</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.789198494906578</v>
+        <v>2.832313249644233</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.119411884495759</v>
+        <v>-3.047553959932999</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.218469390497546</v>
+        <v>1.24721256032265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.7140018674801818</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.851876934360051</v>
+        <v>2.894991689097706</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.007034883313086</v>
+        <v>-2.935176958750327</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.268911486801282</v>
+        <v>1.297654656626386</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.7140018674801818</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.857368230190718</v>
+        <v>2.900482984928373</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.034815281214439</v>
+        <v>-2.96295735665168</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.26929652940928</v>
+        <v>1.298039699234384</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6143635450160698</v>
+        <v>0.6862214695788287</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.852197193218445</v>
+        <v>2.895311947956101</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.117816562239718</v>
+        <v>-3.045958637676959</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.074451736999822</v>
+        <v>1.103194906824926</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.679410382502794</v>
+        <v>2.72252513724045</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.226430640683049</v>
+        <v>-3.15457271612029</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.151155766341695</v>
+        <v>1.179898936166799</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.799560043222</v>
+        <v>2.842674797959655</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.191021602434907</v>
+        <v>-3.119163677872147</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.179832407743275</v>
+        <v>1.208575577568379</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.814073069324323</v>
+        <v>2.857187824061978</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.152637939876755</v>
+        <v>-3.080780015313996</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.192605314108904</v>
+        <v>1.221348483934008</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.7060342476098062</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834522708201582</v>
+        <v>2.877637462939238</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.975521609841589</v>
+        <v>-2.90366368527883</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.260180874968273</v>
+        <v>1.288924044793376</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.7060342476098062</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831251737046884</v>
+        <v>2.87436649178454</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.020613854675135</v>
+        <v>-2.948755930112376</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.242827368796767</v>
+        <v>1.271570538621871</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5722802798776575</v>
+        <v>0.6441382044404164</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794797502907163</v>
+        <v>2.837912257644819</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.841238433436367</v>
+        <v>-2.769380508873608</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.308364512598689</v>
+        <v>1.337107682423793</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7290570380483762</v>
+        <v>0.800914962611135</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.882650533116009</v>
+        <v>2.925765287853664</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.886252646956974</v>
+        <v>-2.814394722394214</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.271166282522036</v>
+        <v>1.29990945234714</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6987081427337716</v>
+        <v>0.7705660672965304</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845248651258836</v>
+        <v>2.888363405996492</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.153257157229409</v>
+        <v>-3.08139923266665</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.170056040752008</v>
+        <v>1.198799210577111</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5043451046908229</v>
+        <v>0.5762030292535818</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734322390772013</v>
+        <v>2.777437145509668</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.254454938666582</v>
+        <v>-3.182597014103822</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.12878085007364</v>
+        <v>1.157524019898744</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5077942157082627</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692481024541323</v>
+        <v>2.735595779278978</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.247943972052269</v>
+        <v>-3.17608604748951</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.128985198273682</v>
+        <v>1.157728368098786</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5077942157082627</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.690080986095639</v>
+        <v>2.733195740833295</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.228905844344972</v>
+        <v>-3.157047919782213</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.133125168564846</v>
+        <v>1.161868338389949</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4496106043770681</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651695538505167</v>
+        <v>2.694810293242823</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.26003247549559</v>
+        <v>-3.188174550932831</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.298256385043279</v>
+        <v>1.326999554868383</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4496106043770681</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.829277407443848</v>
+        <v>2.872392162181503</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.273899236829507</v>
+        <v>-3.202041312266748</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.293543009495846</v>
+        <v>1.322286179320949</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.4117526876432452</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.807395986389688</v>
+        <v>2.850510741127343</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.229095065289577</v>
+        <v>-3.157237140726818</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.317473208508743</v>
+        <v>1.346216378333847</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.4117526876432452</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.813404516786614</v>
+        <v>2.856519271524269</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.081352095054575</v>
+        <v>-3.009494170491816</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.274520617879944</v>
+        <v>1.303263787705047</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5795600448781284</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.812039152404743</v>
+        <v>2.855153907142399</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.183366777585796</v>
+        <v>-3.111508853023037</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.236508366398936</v>
+        <v>1.26525153622404</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5795600448781284</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814832773936224</v>
+        <v>2.85794752867388</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.177214071533012</v>
+        <v>-3.105356146970252</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239631797211709</v>
+        <v>1.268374967036812</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5138548263681537</v>
+        <v>0.5857127509309127</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.819186745959553</v>
+        <v>2.862301500697209</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.194023369683513</v>
+        <v>-3.122165445120754</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.231988554691618</v>
+        <v>1.260731724516722</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5689034527804111</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.808181643809362</v>
+        <v>2.851296398547018</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.131725370907391</v>
+        <v>-3.059867446344632</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.323243307998888</v>
+        <v>1.351986477823992</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5689034527804111</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.874517197606183</v>
+        <v>2.917631952343839</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.929935173242233</v>
+        <v>-2.858077248679474</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.206251388779078</v>
+        <v>1.234994558604182</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6950637203868064</v>
+        <v>0.7669216449495655</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.795620114621803</v>
+        <v>2.838734869359458</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.765122170163386</v>
+        <v>-2.693264245600627</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.342466822332792</v>
+        <v>1.371209992157896</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8598767234656534</v>
+        <v>0.9317346480284124</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.964798148791286</v>
+        <v>3.007912903528942</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.862862714788361</v>
+        <v>-2.791004790225601</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.317998340598846</v>
+        <v>1.34674151042395</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8439874453326732</v>
+        <v>0.9158453698954323</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.969892318027542</v>
+        <v>3.013007072765197</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.03920047491129</v>
+        <v>-2.967342550348531</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.245999217374346</v>
+        <v>1.27474238719945</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6676496852097438</v>
+        <v>0.7395076097725028</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.862625642778456</v>
+        <v>2.905740397516111</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.962778428479363</v>
+        <v>-2.890920503916604</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.275059653987045</v>
+        <v>1.303802823812149</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6676496852097438</v>
+        <v>0.7395076097725028</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861117260818384</v>
+        <v>2.904232015556039</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.918405296840795</v>
+        <v>-2.846547372278035</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.292671774077909</v>
+        <v>1.321414943903013</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7120228168483124</v>
+        <v>0.7838807414110714</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.887604007236962</v>
+        <v>2.930718761974617</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.795571075953627</v>
+        <v>-2.723713151390868</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.336199256571366</v>
+        <v>1.36494242639647</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7120228168483124</v>
+        <v>0.7838807414110714</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.881997801375552</v>
+        <v>2.925112556113207</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.747915345392571</v>
+        <v>-2.676057420829812</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.361643305823593</v>
+        <v>1.390386475648697</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.759678547409368</v>
+        <v>0.8315364719721271</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.91697299673999</v>
+        <v>2.960087751477646</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.647397186893817</v>
+        <v>-2.575539262331057</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.40674294259782</v>
+        <v>1.435486112422924</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8601967059081226</v>
+        <v>0.9320546304708817</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.982176265213968</v>
+        <v>3.025291019951623</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.708063777296206</v>
+        <v>-2.636205852733446</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.369230978912737</v>
+        <v>1.39797414873784</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7784983891895889</v>
+        <v>0.850356313752348</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.91991194765872</v>
+        <v>2.963026702396375</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.663225375687808</v>
+        <v>-2.591367451125048</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.391264042166724</v>
+        <v>1.420007211991828</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7830418221344584</v>
+        <v>0.8548997466972175</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.92673571003627</v>
+        <v>2.969850464773925</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.763984011444806</v>
+        <v>-2.692126086882047</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.355121527495003</v>
+        <v>1.383864697320107</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.694216253407453</v>
+        <v>0.766074177970212</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.877601308431145</v>
+        <v>2.9207160631688</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.719781174358906</v>
+        <v>-2.647923249796146</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.3786822648572</v>
+        <v>1.407425434682304</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7384190904933534</v>
+        <v>0.8102770150561125</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.910002613210522</v>
+        <v>2.953117367948177</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.756760202022349</v>
+        <v>-2.68490227745959</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.362300654261071</v>
+        <v>1.391043824086174</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7753929922846839</v>
+        <v>0.847250916847443</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.930596954754568</v>
+        <v>2.973711709492223</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.598468784483077</v>
+        <v>-2.526610859920317</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.476864986459819</v>
+        <v>1.505608156284923</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7753929922846839</v>
+        <v>0.847250916847443</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.981844719937608</v>
+        <v>3.024959474675263</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.390826780848601</v>
+        <v>-2.318968856285841</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.558362492507863</v>
+        <v>1.587105662332966</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9830349959191601</v>
+        <v>1.054892920481919</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.104870626712547</v>
+        <v>3.147985381450202</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.339794688126072</v>
+        <v>-2.267936763563313</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.573723557835144</v>
+        <v>1.602466727660248</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.034067088641688</v>
+        <v>1.105925013204447</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.130438110584334</v>
+        <v>3.173552865321989</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.274570506998867</v>
+        <v>-2.202712582436107</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.617000634378731</v>
+        <v>1.645743804203835</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.099291269768894</v>
+        <v>1.171149194331653</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.186760023353362</v>
+        <v>3.229874778091017</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.237143486927733</v>
+        <v>-2.165285562364974</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.627932414706465</v>
+        <v>1.656675584531569</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.104542807798075</v>
+        <v>1.176400732360835</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.185871918470151</v>
+        <v>3.228986673207807</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.257255142962441</v>
+        <v>-2.185397218399682</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.621144544623822</v>
+        <v>1.649887714448926</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.115570152795495</v>
+        <v>1.187428077358254</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.193745117799843</v>
+        <v>3.236859872537499</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.203510328535236</v>
+        <v>-2.131652403972477</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.803200241415915</v>
+        <v>1.831943411241018</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.125633462235957</v>
+        <v>1.197491386798716</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.360340874485331</v>
+        <v>3.403455629222986</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.179718759929094</v>
+        <v>-2.107860835366335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.932829778076189</v>
+        <v>1.961572947901293</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.149425030842099</v>
+        <v>1.221282955404858</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.494728724866834</v>
+        <v>3.537843479604489</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.153634675665286</v>
+        <v>-2.081776751102527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.934971387795571</v>
+        <v>1.963714557620675</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.149425030842099</v>
+        <v>1.221282955404858</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.486436700880692</v>
+        <v>3.529551455618348</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.075503494816339</v>
+        <v>-2.00364557025358</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.964417055718929</v>
+        <v>1.993160225544033</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.223601841725784</v>
+        <v>1.295459766288543</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.529135982994683</v>
+        <v>3.572250737732338</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.066611033423056</v>
+        <v>-1.994753108860297</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.985528446003034</v>
+        <v>2.014271615828138</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.223601841725784</v>
+        <v>1.295459766288543</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.546690388721474</v>
+        <v>3.58980514345913</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.235087150392934</v>
+        <v>-2.163229225830174</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.909993046619667</v>
+        <v>1.938736216444771</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.195654006009203</v>
+        <v>1.267511930571962</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.52177673469611</v>
+        <v>3.564891489433765</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.537287621531351</v>
+        <v>-1.465429696968591</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.170382555352162</v>
+        <v>2.199125725177265</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.125305946638792</v>
+        <v>1.197163871201552</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.460837596261725</v>
+        <v>3.503952350999381</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.514566517848198</v>
+        <v>-1.442708593285439</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.170135019322327</v>
+        <v>2.198878189147431</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.125305946638792</v>
+        <v>1.197163871201552</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.45150161875863</v>
+        <v>3.494616373496285</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.512841474558155</v>
+        <v>-1.440983549995395</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.329731162489514</v>
+        <v>2.358474332314618</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.127030989928836</v>
+        <v>1.198888914491595</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.611442770583825</v>
+        <v>3.654557525321481</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.66762248133641</v>
+        <v>-1.59576455677365</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.304896582271859</v>
+        <v>2.333639752096962</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.09366331587436</v>
+        <v>1.165521240437119</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.628499988644786</v>
+        <v>3.671614743382441</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.61618714795175</v>
+        <v>-1.544329223388991</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.322146071615268</v>
+        <v>2.350889241440371</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.145098649259019</v>
+        <v>1.216956573821779</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.656036544665127</v>
+        <v>3.699151299402782</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.589235923625262</v>
+        <v>-1.517377999062503</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.342932714990604</v>
+        <v>2.371675884815708</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.159978995286739</v>
+        <v>1.231836919849498</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.6749709059265</v>
+        <v>3.718085660664155</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.725188931681578</v>
+        <v>-1.653331007118819</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.472654643913037</v>
+        <v>2.501397813738141</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.159978995286739</v>
+        <v>1.231836919849498</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.859074038071459</v>
+        <v>3.902188792809115</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.747597049486451</v>
+        <v>-1.675739124923691</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.455808091694082</v>
+        <v>2.484551261519186</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.159978995286739</v>
+        <v>1.231836919849498</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.851190732974453</v>
+        <v>3.894305487712108</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.89560281696585</v>
+        <v>-1.82374489240309</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.398659784251959</v>
+        <v>2.427402954077063</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.073251986423197</v>
+        <v>1.145109910985956</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.801208527205965</v>
+        <v>3.844323281943621</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.90504374285438</v>
+        <v>-1.83318581829162</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.451137131618395</v>
+        <v>2.479880301443498</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.195679103966588</v>
+        <v>1.267537028529348</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.930918515453847</v>
+        <v>3.974033270191502</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.903756979314823</v>
+        <v>-1.831899054752063</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.454542931579518</v>
+        <v>2.483286101404622</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.196965867506145</v>
+        <v>1.268823792068904</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.934581668122882</v>
+        <v>3.977696422860538</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.905314033304114</v>
+        <v>-1.833456108741355</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.452031922877577</v>
+        <v>2.480775092702681</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.196965867506145</v>
+        <v>1.268823792068904</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.932693481016657</v>
+        <v>3.975808235754313</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.912585918827579</v>
+        <v>-1.840727994264819</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.443943398271053</v>
+        <v>2.472686568096157</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.18969398198268</v>
+        <v>1.261551906545439</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.923150579305441</v>
+        <v>3.966265334043096</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.910744899769328</v>
+        <v>-1.838886975206568</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.443113816104506</v>
+        <v>2.47185698592961</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.190962208654148</v>
+        <v>1.262820133216908</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.922345525518474</v>
+        <v>3.96546028025613</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.917653605269008</v>
+        <v>-1.845795680706248</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.453423740770552</v>
+        <v>2.482166910595656</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.190962208654148</v>
+        <v>1.262820133216908</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.935418932384392</v>
+        <v>3.978533687122048</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.919215248083868</v>
+        <v>-1.847357323521108</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.452799083644609</v>
+        <v>2.481542253469712</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.190962208654148</v>
+        <v>1.262820133216908</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.935418932384392</v>
+        <v>3.978533687122048</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.947116035193341</v>
+        <v>-1.875258110630581</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.440162809927822</v>
+        <v>2.468905979752925</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.156365284511214</v>
+        <v>1.228223209073973</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913184819025633</v>
+        <v>3.956299573763289</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.950149032706015</v>
+        <v>-1.878291108143255</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.435714054899951</v>
+        <v>2.464457224725054</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.15333228699854</v>
+        <v>1.225190211561299</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.908129464495228</v>
+        <v>3.951244219232883</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.970210353982522</v>
+        <v>-1.898352429419762</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.494395485979851</v>
+        <v>2.523138655804955</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.133270965722033</v>
+        <v>1.205128890284792</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.962798631319828</v>
+        <v>4.005913386057483</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.226931171977346</v>
+        <v>-2.155073247414586</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.532018877783769</v>
+        <v>2.560762047608873</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.024856391578218</v>
+        <v>1.096714316140977</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.038061605835385</v>
+        <v>4.081176360573041</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.380917589753486</v>
+        <v>-2.309059665190726</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.539404579818953</v>
+        <v>2.568147749644056</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.024856391578218</v>
+        <v>1.096714316140977</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.107041874981025</v>
+        <v>4.150156629718681</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.33039568592582</v>
+        <v>-2.258537761363061</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.54566454347014</v>
+        <v>2.574407713295244</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.024856391578218</v>
+        <v>1.096714316140977</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.093093077101146</v>
+        <v>4.136207831838802</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.582870839933545</v>
+        <v>-2.511012915370785</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.456544970922464</v>
+        <v>2.485288140747568</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.024856391578218</v>
+        <v>1.096714316140977</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.10496356615656</v>
+        <v>4.148078320894216</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.852343641855253</v>
+        <v>-2.780485717292493</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.349966384672725</v>
+        <v>2.378709554497828</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.024856391578218</v>
+        <v>1.096714316140977</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.106174100675504</v>
+        <v>4.149288855413159</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.009887713584694</v>
+        <v>-2.938029789021934</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.29107049820827</v>
+        <v>2.319813668033373</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9579545864379435</v>
+        <v>1.029812511000703</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.070154759818661</v>
+        <v>4.113269514556317</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.138738264286741</v>
+        <v>-3.066880339723981</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.234608130663641</v>
+        <v>2.263351300488744</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.916961177587222</v>
+        <v>0.9888191021499813</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.040636567244417</v>
+        <v>4.083751321982072</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.788292888427046</v>
+        <v>3.797317555639916</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.25131802042395</v>
+        <v>-3.249730279287618</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.351780284907801</v>
+        <v>2.352415381362333</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.916961177587222</v>
+        <v>0.9888191021499813</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.202840623943461</v>
+        <v>4.245955378681117</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-64.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.7%</t>
+          <t>459.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-486.5%</t>
+          <t>-464.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.0%</t>
+          <t>-132.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.9%</t>
+          <t>-131.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-125.1%</t>
+          <t>-121.3%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.280402348419501</v>
+        <v>-3.35226027298226</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.23040502311674</v>
+        <v>1.201661853291636</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.899154266877326</v>
+        <v>2.856039512139671</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.220549729215778</v>
+        <v>-3.292407653778537</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.264518457230362</v>
+        <v>1.235775287405258</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.909326653309459</v>
+        <v>2.866211898571803</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.1343062661894</v>
+        <v>-3.206164190752159</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.293962113014773</v>
+        <v>1.265218943189669</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.904272923883319</v>
+        <v>2.861158169145663</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.17961308558838</v>
+        <v>-3.251471010151139</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.267615160699707</v>
+        <v>1.238871990874603</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5529096371225</v>
+        <v>0.481051712559741</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.871562601522306</v>
+        <v>2.828447846784651</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.208646190290681</v>
+        <v>-3.280504114853441</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.256553791851887</v>
+        <v>1.227810622026784</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5529096371225</v>
+        <v>0.481051712559741</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.872114474555408</v>
+        <v>2.828999719817752</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.115835708839822</v>
+        <v>-3.187693633402581</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.222950676323597</v>
+        <v>1.194207506498493</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6457201185733593</v>
+        <v>0.5738621940106003</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.857073455317289</v>
+        <v>2.813958700579633</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.16022517816925</v>
+        <v>-3.232083102732009</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.207068364516427</v>
+        <v>1.178325194691323</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6013306492439316</v>
+        <v>0.5294727246811727</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.832313249644233</v>
+        <v>2.789198494906578</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.047553959932999</v>
+        <v>-3.119411884495759</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.24721256032265</v>
+        <v>1.218469390497546</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7140018674801818</v>
+        <v>0.6421439429174229</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.894991689097706</v>
+        <v>2.851876934360051</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.935176958750327</v>
+        <v>-3.007034883313086</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.297654656626386</v>
+        <v>1.268911486801282</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7140018674801818</v>
+        <v>0.6421439429174229</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.900482984928373</v>
+        <v>2.857368230190718</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.96295735665168</v>
+        <v>-3.034815281214439</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.298039699234384</v>
+        <v>1.26929652940928</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6862214695788287</v>
+        <v>0.6143635450160698</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.895311947956101</v>
+        <v>2.852197193218445</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.045958637676959</v>
+        <v>-3.117816562239718</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.103194906824926</v>
+        <v>1.074451736999822</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.72252513724045</v>
+        <v>2.679410382502794</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.15457271612029</v>
+        <v>-3.226430640683049</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.179898936166799</v>
+        <v>1.151155766341695</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.842674797959655</v>
+        <v>2.799560043222</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.119163677872147</v>
+        <v>-3.191021602434907</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.208575577568379</v>
+        <v>1.179832407743275</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.857187824061978</v>
+        <v>2.814073069324323</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.080780015313996</v>
+        <v>-3.152637939876755</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.221348483934008</v>
+        <v>1.192605314108904</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7060342476098062</v>
+        <v>0.6341763230470473</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.877637462939238</v>
+        <v>2.834522708201582</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.90366368527883</v>
+        <v>-2.975521609841589</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.288924044793376</v>
+        <v>1.260180874968273</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7060342476098062</v>
+        <v>0.6341763230470473</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.87436649178454</v>
+        <v>2.831251737046884</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.948755930112376</v>
+        <v>-3.020613854675135</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.271570538621871</v>
+        <v>1.242827368796767</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6441382044404164</v>
+        <v>0.5722802798776575</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.837912257644819</v>
+        <v>2.794797502907163</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.769380508873608</v>
+        <v>-2.841238433436367</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.337107682423793</v>
+        <v>1.308364512598689</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.800914962611135</v>
+        <v>0.7290570380483762</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.925765287853664</v>
+        <v>2.882650533116009</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.814394722394214</v>
+        <v>-2.886252646956974</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.29990945234714</v>
+        <v>1.271166282522036</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7705660672965304</v>
+        <v>0.6987081427337716</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.888363405996492</v>
+        <v>2.845248651258836</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.08139923266665</v>
+        <v>-3.153257157229409</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.198799210577111</v>
+        <v>1.170056040752008</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5762030292535818</v>
+        <v>0.5043451046908229</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.777437145509668</v>
+        <v>2.734322390772013</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.182597014103822</v>
+        <v>-3.254454938666582</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.157524019898744</v>
+        <v>1.12878085007364</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5077942157082627</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.735595779278978</v>
+        <v>2.692481024541323</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.17608604748951</v>
+        <v>-3.247943972052269</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.157728368098786</v>
+        <v>1.128985198273682</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5077942157082627</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.733195740833295</v>
+        <v>2.690080986095639</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.157047919782213</v>
+        <v>-3.228905844344972</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.161868338389949</v>
+        <v>1.133125168564846</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4496106043770681</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.694810293242823</v>
+        <v>2.651695538505167</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.188174550932831</v>
+        <v>-3.26003247549559</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.326999554868383</v>
+        <v>1.298256385043279</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4496106043770681</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.872392162181503</v>
+        <v>2.829277407443848</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.202041312266748</v>
+        <v>-3.273899236829507</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.322286179320949</v>
+        <v>1.293543009495846</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4117526876432452</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850510741127343</v>
+        <v>2.807395986389688</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.157237140726818</v>
+        <v>-3.229095065289577</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.346216378333847</v>
+        <v>1.317473208508743</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4117526876432452</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856519271524269</v>
+        <v>2.813404516786614</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.009494170491816</v>
+        <v>-3.081352095054575</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.303263787705047</v>
+        <v>1.274520617879944</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5795600448781284</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855153907142399</v>
+        <v>2.812039152404743</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.111508853023037</v>
+        <v>-3.183366777585796</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.26525153622404</v>
+        <v>1.236508366398936</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5795600448781284</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.85794752867388</v>
+        <v>2.814832773936224</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.105356146970252</v>
+        <v>-3.177214071533012</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.268374967036812</v>
+        <v>1.239631797211709</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5857127509309127</v>
+        <v>0.5138548263681537</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862301500697209</v>
+        <v>2.819186745959553</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.122165445120754</v>
+        <v>-3.194023369683513</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.260731724516722</v>
+        <v>1.231988554691618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5689034527804111</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851296398547018</v>
+        <v>2.808181643809362</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.059867446344632</v>
+        <v>-3.131725370907391</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.351986477823992</v>
+        <v>1.323243307998888</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5689034527804111</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.917631952343839</v>
+        <v>2.874517197606183</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.858077248679474</v>
+        <v>-2.929935173242233</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.234994558604182</v>
+        <v>1.206251388779078</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7669216449495655</v>
+        <v>0.6950637203868064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.838734869359458</v>
+        <v>2.795620114621803</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.693264245600627</v>
+        <v>-2.765122170163386</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.371209992157896</v>
+        <v>1.342466822332792</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9317346480284124</v>
+        <v>0.8598767234656534</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.007912903528942</v>
+        <v>2.964798148791286</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.791004790225601</v>
+        <v>-2.862862714788361</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.34674151042395</v>
+        <v>1.317998340598846</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9158453698954323</v>
+        <v>0.8439874453326732</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.013007072765197</v>
+        <v>2.969892318027542</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.967342550348531</v>
+        <v>-3.03920047491129</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.27474238719945</v>
+        <v>1.245999217374346</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7395076097725028</v>
+        <v>0.6676496852097438</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.905740397516111</v>
+        <v>2.862625642778456</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.890920503916604</v>
+        <v>-2.962778428479363</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.303802823812149</v>
+        <v>1.275059653987045</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7395076097725028</v>
+        <v>0.6676496852097438</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.904232015556039</v>
+        <v>2.861117260818384</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.846547372278035</v>
+        <v>-2.918405296840795</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.321414943903013</v>
+        <v>1.292671774077909</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7838807414110714</v>
+        <v>0.7120228168483124</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.930718761974617</v>
+        <v>2.887604007236962</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.723713151390868</v>
+        <v>-2.795571075953627</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.36494242639647</v>
+        <v>1.336199256571366</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7838807414110714</v>
+        <v>0.7120228168483124</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.925112556113207</v>
+        <v>2.881997801375552</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.676057420829812</v>
+        <v>-2.747915345392571</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.390386475648697</v>
+        <v>1.361643305823593</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8315364719721271</v>
+        <v>0.759678547409368</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.960087751477646</v>
+        <v>2.91697299673999</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.575539262331057</v>
+        <v>-2.647397186893817</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.435486112422924</v>
+        <v>1.40674294259782</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9320546304708817</v>
+        <v>0.8601967059081226</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.025291019951623</v>
+        <v>2.982176265213968</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.636205852733446</v>
+        <v>-2.708063777296206</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.39797414873784</v>
+        <v>1.369230978912737</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.850356313752348</v>
+        <v>0.7784983891895889</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.963026702396375</v>
+        <v>2.91991194765872</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.591367451125048</v>
+        <v>-2.663225375687808</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.420007211991828</v>
+        <v>1.391264042166724</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8548997466972175</v>
+        <v>0.7830418221344584</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.969850464773925</v>
+        <v>2.92673571003627</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.692126086882047</v>
+        <v>-2.763984011444806</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.383864697320107</v>
+        <v>1.355121527495003</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.766074177970212</v>
+        <v>0.694216253407453</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.9207160631688</v>
+        <v>2.877601308431145</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.647923249796146</v>
+        <v>-2.719781174358906</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.407425434682304</v>
+        <v>1.3786822648572</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8102770150561125</v>
+        <v>0.7384190904933534</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.953117367948177</v>
+        <v>2.910002613210522</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.68490227745959</v>
+        <v>-2.756760202022349</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.391043824086174</v>
+        <v>1.362300654261071</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.847250916847443</v>
+        <v>0.7753929922846839</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.973711709492223</v>
+        <v>2.930596954754568</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.526610859920317</v>
+        <v>-2.598468784483077</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.505608156284923</v>
+        <v>1.476864986459819</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.847250916847443</v>
+        <v>0.7753929922846839</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.024959474675263</v>
+        <v>2.981844719937608</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.318968856285841</v>
+        <v>-2.390826780848601</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.587105662332966</v>
+        <v>1.558362492507863</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.054892920481919</v>
+        <v>0.9830349959191601</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.147985381450202</v>
+        <v>3.104870626712547</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.267936763563313</v>
+        <v>-2.339794688126072</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.602466727660248</v>
+        <v>1.573723557835144</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.105925013204447</v>
+        <v>1.034067088641688</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.173552865321989</v>
+        <v>3.130438110584334</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.202712582436107</v>
+        <v>-2.274570506998867</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.645743804203835</v>
+        <v>1.617000634378731</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.171149194331653</v>
+        <v>1.099291269768894</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.229874778091017</v>
+        <v>3.186760023353362</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.165285562364974</v>
+        <v>-2.237143486927733</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.656675584531569</v>
+        <v>1.627932414706465</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.176400732360835</v>
+        <v>1.104542807798075</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.228986673207807</v>
+        <v>3.185871918470151</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.185397218399682</v>
+        <v>-2.257255142962441</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.649887714448926</v>
+        <v>1.621144544623822</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.187428077358254</v>
+        <v>1.115570152795495</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.236859872537499</v>
+        <v>3.193745117799843</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.131652403972477</v>
+        <v>-2.128486473257627</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.831943411241018</v>
+        <v>1.833209783526959</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.197491386798716</v>
+        <v>1.148612071933981</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.403455629222986</v>
+        <v>3.374128040304146</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.107860835366335</v>
+        <v>-2.104694904651485</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.961572947901293</v>
+        <v>1.962839320187233</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.221282955404858</v>
+        <v>1.172403640540124</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.537843479604489</v>
+        <v>3.508515890685648</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.081776751102527</v>
+        <v>-2.078610820387677</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.963714557620675</v>
+        <v>1.964980929906615</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.221282955404858</v>
+        <v>1.172403640540124</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.529551455618348</v>
+        <v>3.500223866699507</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.00364557025358</v>
+        <v>-2.00047963953873</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.993160225544033</v>
+        <v>1.994426597829973</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.295459766288543</v>
+        <v>1.246580451423808</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.572250737732338</v>
+        <v>3.542923148813498</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.994753108860297</v>
+        <v>-1.991587178145447</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.014271615828138</v>
+        <v>2.015537988114078</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.295459766288543</v>
+        <v>1.246580451423808</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.58980514345913</v>
+        <v>3.560477554540289</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.163229225830174</v>
+        <v>-2.160063295115324</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.938736216444771</v>
+        <v>1.940002588730711</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.267511930571962</v>
+        <v>1.218632615707228</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.564891489433765</v>
+        <v>3.535563900514925</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.465429696968591</v>
+        <v>-1.462263766253741</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.199125725177265</v>
+        <v>2.200392097463205</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.197163871201552</v>
+        <v>1.148284556336817</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.503952350999381</v>
+        <v>3.47462476208054</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.442708593285439</v>
+        <v>-1.439542662570588</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.198878189147431</v>
+        <v>2.200144561433371</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.197163871201552</v>
+        <v>1.148284556336817</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.494616373496285</v>
+        <v>3.465288784577444</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.440983549995395</v>
+        <v>-1.437817619280545</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.358474332314618</v>
+        <v>2.359740704600558</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.198888914491595</v>
+        <v>1.150009599626861</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.654557525321481</v>
+        <v>3.62522993640264</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.59576455677365</v>
+        <v>-1.364617880145367</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.333639752096962</v>
+        <v>2.426098422748276</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.165521240437119</v>
+        <v>1.203618453571715</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.671614743382441</v>
+        <v>3.694473071263199</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.544329223388991</v>
+        <v>-1.313182546760707</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.350889241440371</v>
+        <v>2.443347912091685</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.216956573821779</v>
+        <v>1.255053786956375</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.699151299402782</v>
+        <v>3.72200962728354</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.517377999062503</v>
+        <v>-1.286231322434219</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.371675884815708</v>
+        <v>2.464134555467021</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.231836919849498</v>
+        <v>1.269934132984094</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.718085660664155</v>
+        <v>3.740943988544913</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.653331007118819</v>
+        <v>-1.422184330490535</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.501397813738141</v>
+        <v>2.593856484389454</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.231836919849498</v>
+        <v>1.269934132984094</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.902188792809115</v>
+        <v>3.925047120689872</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.675739124923691</v>
+        <v>-1.444592448295407</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.484551261519186</v>
+        <v>2.577009932170499</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.231836919849498</v>
+        <v>1.269934132984094</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.894305487712108</v>
+        <v>3.917163815592866</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.82374489240309</v>
+        <v>-1.592598215774806</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.427402954077063</v>
+        <v>2.519861624728377</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.145109910985956</v>
+        <v>1.183207124120553</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.844323281943621</v>
+        <v>3.867181609824379</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.83318581829162</v>
+        <v>-1.602039141663336</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.479880301443498</v>
+        <v>2.572338972094812</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.267537028529348</v>
+        <v>1.305634241663944</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.974033270191502</v>
+        <v>3.99689159807226</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.831899054752063</v>
+        <v>-1.600752378123779</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.483286101404622</v>
+        <v>2.575744772055935</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.268823792068904</v>
+        <v>1.306921005203501</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.977696422860538</v>
+        <v>4.000554750741295</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.833456108741355</v>
+        <v>-1.602309432113071</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.480775092702681</v>
+        <v>2.573233763353994</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.268823792068904</v>
+        <v>1.306921005203501</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.975808235754313</v>
+        <v>3.99866656363507</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.840727994264819</v>
+        <v>-1.609581317636535</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.472686568096157</v>
+        <v>2.56514523874747</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.261551906545439</v>
+        <v>1.299649119680036</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.966265334043096</v>
+        <v>3.989123661923854</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.838886975206568</v>
+        <v>-1.607740298578284</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.47185698592961</v>
+        <v>2.564315656580924</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.262820133216908</v>
+        <v>1.300917346351504</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.96546028025613</v>
+        <v>3.988318608136887</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.845795680706248</v>
+        <v>-1.614649004077964</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.482166910595656</v>
+        <v>2.57462558124697</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.262820133216908</v>
+        <v>1.300917346351504</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.978533687122048</v>
+        <v>4.001392015002805</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.847357323521108</v>
+        <v>-1.616210646892824</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.481542253469712</v>
+        <v>2.574000924121026</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.262820133216908</v>
+        <v>1.300917346351504</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.978533687122048</v>
+        <v>4.001392015002805</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.875258110630581</v>
+        <v>-1.644111434002297</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.468905979752925</v>
+        <v>2.561364650404239</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.228223209073973</v>
+        <v>1.266320422208569</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.956299573763289</v>
+        <v>3.979157901644047</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.878291108143255</v>
+        <v>-1.647144431514971</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.464457224725054</v>
+        <v>2.556915895376368</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.225190211561299</v>
+        <v>1.263287424695895</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.951244219232883</v>
+        <v>3.974102547113642</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.898352429419762</v>
+        <v>-1.667205752791478</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.523138655804955</v>
+        <v>2.615597326456269</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.205128890284792</v>
+        <v>1.243226103419388</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.005913386057483</v>
+        <v>4.028771713938241</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.155073247414586</v>
+        <v>-1.923926570786302</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.560762047608873</v>
+        <v>2.653220718260186</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.096714316140977</v>
+        <v>1.134811529275574</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.081176360573041</v>
+        <v>4.104034688453799</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.309059665190726</v>
+        <v>-2.077912988562443</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.568147749644056</v>
+        <v>2.66060642029537</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.096714316140977</v>
+        <v>1.134811529275574</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.150156629718681</v>
+        <v>4.173014957599439</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.258537761363061</v>
+        <v>-2.027391084734777</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.574407713295244</v>
+        <v>2.666866383946557</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.096714316140977</v>
+        <v>1.134811529275574</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.136207831838802</v>
+        <v>4.15906615971956</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.511012915370785</v>
+        <v>-2.279866238742501</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.485288140747568</v>
+        <v>2.577746811398881</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.096714316140977</v>
+        <v>1.134811529275574</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.148078320894216</v>
+        <v>4.170936648774973</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.780485717292493</v>
+        <v>-2.549339040664209</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.378709554497828</v>
+        <v>2.471168225149142</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.096714316140977</v>
+        <v>1.134811529275574</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.149288855413159</v>
+        <v>4.172147183293918</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.938029789021934</v>
+        <v>-2.70688311239365</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.319813668033373</v>
+        <v>2.412272338684687</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.029812511000703</v>
+        <v>1.067909724135299</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.113269514556317</v>
+        <v>4.136127842437074</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.066880339723981</v>
+        <v>-2.835733663095697</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.263351300488744</v>
+        <v>2.355809971140058</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.9888191021499813</v>
+        <v>1.026916315284577</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.083751321982072</v>
+        <v>4.106609649862831</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.797317555639916</v>
+        <v>3.867083857469643</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.249730279287618</v>
+        <v>-3.02717637878104</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.352415381362333</v>
+        <v>2.441436941564965</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.9888191021499813</v>
+        <v>1.026916315284577</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.245955378681117</v>
+        <v>4.268813706561875</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-69.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.2%</t>
+          <t>-64.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.2%</t>
+          <t>459.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.3%</t>
+          <t>-123.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-20.5%</t>
         </is>
       </c>
     </row>
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.128486473257627</v>
+        <v>-2.203510328535236</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.833209783526959</v>
+        <v>1.803200241415915</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.148612071933981</v>
+        <v>1.125633462235957</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.374128040304146</v>
+        <v>3.360340874485331</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.104694904651485</v>
+        <v>-2.179718759929094</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.962839320187233</v>
+        <v>1.932829778076189</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.172403640540124</v>
+        <v>1.149425030842099</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.508515890685648</v>
+        <v>3.494728724866834</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.078610820387677</v>
+        <v>-2.153634675665286</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.964980929906615</v>
+        <v>1.934971387795571</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.172403640540124</v>
+        <v>1.149425030842099</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.500223866699507</v>
+        <v>3.486436700880692</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.00047963953873</v>
+        <v>-2.075503494816339</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.994426597829973</v>
+        <v>1.964417055718929</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.246580451423808</v>
+        <v>1.223601841725784</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.542923148813498</v>
+        <v>3.529135982994683</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.991587178145447</v>
+        <v>-2.066611033423056</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.015537988114078</v>
+        <v>1.985528446003034</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.246580451423808</v>
+        <v>1.223601841725784</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.560477554540289</v>
+        <v>3.546690388721474</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.160063295115324</v>
+        <v>-2.235087150392934</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.940002588730711</v>
+        <v>1.909993046619667</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.218632615707228</v>
+        <v>1.195654006009203</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.535563900514925</v>
+        <v>3.52177673469611</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.462263766253741</v>
+        <v>-1.537287621531351</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.200392097463205</v>
+        <v>2.170382555352162</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.148284556336817</v>
+        <v>1.125305946638792</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.47462476208054</v>
+        <v>3.460837596261725</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.439542662570588</v>
+        <v>-1.514566517848198</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.200144561433371</v>
+        <v>2.170135019322327</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.148284556336817</v>
+        <v>1.125305946638792</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.465288784577444</v>
+        <v>3.45150161875863</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.437817619280545</v>
+        <v>-1.512841474558155</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.359740704600558</v>
+        <v>2.329731162489514</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.150009599626861</v>
+        <v>1.127030989928836</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.62522993640264</v>
+        <v>3.611442770583825</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.364617880145367</v>
+        <v>-1.439240010641333</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.426098422748276</v>
+        <v>2.396249570549889</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.203618453571715</v>
+        <v>1.180228278285245</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.694473071263199</v>
+        <v>3.680438966091317</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.313182546760707</v>
+        <v>-1.387804677256674</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.443347912091685</v>
+        <v>2.413499059893298</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.255053786956375</v>
+        <v>1.231663611669905</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.72200962728354</v>
+        <v>3.707975522111658</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.286231322434219</v>
+        <v>-1.360853452930186</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.464134555467021</v>
+        <v>2.434285703268634</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.269934132984094</v>
+        <v>1.246543957697624</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.740943988544913</v>
+        <v>3.726909883373031</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.422184330490535</v>
+        <v>-1.496806460986502</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.593856484389454</v>
+        <v>2.564007632191068</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.269934132984094</v>
+        <v>1.246543957697624</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.925047120689872</v>
+        <v>3.911013015517991</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.444592448295407</v>
+        <v>-1.519214578791374</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.577009932170499</v>
+        <v>2.547161079972112</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.269934132984094</v>
+        <v>1.246543957697624</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.917163815592866</v>
+        <v>3.903129710420984</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.592598215774806</v>
+        <v>-1.667220346270773</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.519861624728377</v>
+        <v>2.49001277252999</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.183207124120553</v>
+        <v>1.159816948834082</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.867181609824379</v>
+        <v>3.853147504652496</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.602039141663336</v>
+        <v>-1.676661272159303</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.572338972094812</v>
+        <v>2.542490119896425</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.305634241663944</v>
+        <v>1.282244066377474</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.99689159807226</v>
+        <v>3.982857492900378</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.600752378123779</v>
+        <v>-1.675374508619746</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.575744772055935</v>
+        <v>2.545895919857549</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.306921005203501</v>
+        <v>1.28353082991703</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.000554750741295</v>
+        <v>3.986520645569413</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.602309432113071</v>
+        <v>-1.676931562609038</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.573233763353994</v>
+        <v>2.543384911155607</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.306921005203501</v>
+        <v>1.28353082991703</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.99866656363507</v>
+        <v>3.984632458463188</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.609581317636535</v>
+        <v>-1.684203448132503</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.56514523874747</v>
+        <v>2.535296386549084</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.299649119680036</v>
+        <v>1.276258944393565</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.989123661923854</v>
+        <v>3.975089556751971</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.607740298578284</v>
+        <v>-1.682362429074251</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.564315656580924</v>
+        <v>2.534466804382537</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.300917346351504</v>
+        <v>1.277527171065034</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.988318608136887</v>
+        <v>3.974284502965005</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.614649004077964</v>
+        <v>-1.689271134573932</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.57462558124697</v>
+        <v>2.544776729048583</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.300917346351504</v>
+        <v>1.277527171065034</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.001392015002805</v>
+        <v>3.987357909830924</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.616210646892824</v>
+        <v>-1.690832777388791</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.574000924121026</v>
+        <v>2.544152071922639</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.300917346351504</v>
+        <v>1.277527171065034</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.001392015002805</v>
+        <v>3.987357909830924</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.644111434002297</v>
+        <v>-1.718733564498264</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.561364650404239</v>
+        <v>2.531515798205852</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.266320422208569</v>
+        <v>1.242930246922099</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.979157901644047</v>
+        <v>3.965123796472165</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.647144431514971</v>
+        <v>-1.721766562010938</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.556915895376368</v>
+        <v>2.527067043177981</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.263287424695895</v>
+        <v>1.239897249409425</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.974102547113642</v>
+        <v>3.960068441941759</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.667205752791478</v>
+        <v>-1.741827883287445</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.615597326456269</v>
+        <v>2.585748474257882</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.243226103419388</v>
+        <v>1.219835928132918</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.028771713938241</v>
+        <v>4.014737608766358</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.923926570786302</v>
+        <v>-1.998548701282269</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.653220718260186</v>
+        <v>2.6233718660618</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.134811529275574</v>
+        <v>1.111421353989103</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.104034688453799</v>
+        <v>4.090000583281917</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.077912988562443</v>
+        <v>-2.15253511905841</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.66060642029537</v>
+        <v>2.630757568096983</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.134811529275574</v>
+        <v>1.111421353989103</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.173014957599439</v>
+        <v>4.158980852427557</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.027391084734777</v>
+        <v>-2.102013215230744</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.666866383946557</v>
+        <v>2.637017531748171</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.134811529275574</v>
+        <v>1.111421353989103</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.15906615971956</v>
+        <v>4.145032054547677</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.279866238742501</v>
+        <v>-2.354488369238468</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.577746811398881</v>
+        <v>2.547897959200495</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.134811529275574</v>
+        <v>1.111421353989103</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.170936648774973</v>
+        <v>4.156902543603092</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.549339040664209</v>
+        <v>-2.623961171160176</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.471168225149142</v>
+        <v>2.441319372950755</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.134811529275574</v>
+        <v>1.111421353989103</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.172147183293918</v>
+        <v>4.158113078122035</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.70688311239365</v>
+        <v>-2.781505242889617</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.412272338684687</v>
+        <v>2.3824234864863</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.067909724135299</v>
+        <v>1.044519548848829</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.136127842437074</v>
+        <v>4.122093737265192</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.835733663095697</v>
+        <v>-2.910355793591664</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.355809971140058</v>
+        <v>2.325961118941671</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.026916315284577</v>
+        <v>1.003526139998107</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.106609649862831</v>
+        <v>4.092575544690948</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.02717637878104</v>
+        <v>-3.027323486230555</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.441436941564965</v>
+        <v>2.441378098585159</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.026916315284577</v>
+        <v>1.003526139998107</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.268813706561875</v>
+        <v>4.254779601389993</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,17 +786,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.3%</t>
+          <t>-64.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.0%</t>
+          <t>458.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-464.3%</t>
+          <t>-465.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-132.1%</t>
+          <t>-145.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-123.6%</t>
+          <t>-116.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,17 +1456,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-79.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2023"/>
+  <dimension ref="A1:G2024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.35226027298226</v>
+        <v>-3.280402348419501</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.201661853291636</v>
+        <v>1.23040502311674</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.856039512139671</v>
+        <v>2.899154266877326</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.292407653778537</v>
+        <v>-3.220549729215778</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.235775287405258</v>
+        <v>1.264518457230362</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.866211898571803</v>
+        <v>2.909326653309459</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.206164190752159</v>
+        <v>-3.1343062661894</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.265218943189669</v>
+        <v>1.293962113014773</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5937198001317308</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.861158169145663</v>
+        <v>2.904272923883319</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.251471010151139</v>
+        <v>-3.17961308558838</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.238871990874603</v>
+        <v>1.267615160699707</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.481051712559741</v>
+        <v>0.5529096371225</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.828447846784651</v>
+        <v>2.871562601522306</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.280504114853441</v>
+        <v>-3.208646190290681</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.227810622026784</v>
+        <v>1.256553791851887</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.481051712559741</v>
+        <v>0.5529096371225</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.828999719817752</v>
+        <v>2.872114474555408</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.187693633402581</v>
+        <v>-3.115835708839822</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.194207506498493</v>
+        <v>1.222950676323597</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5738621940106003</v>
+        <v>0.6457201185733593</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.813958700579633</v>
+        <v>2.857073455317289</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.232083102732009</v>
+        <v>-3.16022517816925</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.178325194691323</v>
+        <v>1.207068364516427</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5294727246811727</v>
+        <v>0.6013306492439316</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.789198494906578</v>
+        <v>2.832313249644233</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.119411884495759</v>
+        <v>-3.047553959932999</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.218469390497546</v>
+        <v>1.24721256032265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.7140018674801818</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.851876934360051</v>
+        <v>2.894991689097706</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.007034883313086</v>
+        <v>-2.935176958750327</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.268911486801282</v>
+        <v>1.297654656626386</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.7140018674801818</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.857368230190718</v>
+        <v>2.900482984928373</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.034815281214439</v>
+        <v>-2.96295735665168</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.26929652940928</v>
+        <v>1.298039699234384</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6143635450160698</v>
+        <v>0.6862214695788287</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.852197193218445</v>
+        <v>2.895311947956101</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.117816562239718</v>
+        <v>-3.045958637676959</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.074451736999822</v>
+        <v>1.103194906824926</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.679410382502794</v>
+        <v>2.72252513724045</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.226430640683049</v>
+        <v>-3.15457271612029</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.151155766341695</v>
+        <v>1.179898936166799</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.799560043222</v>
+        <v>2.842674797959655</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.191021602434907</v>
+        <v>-3.119163677872147</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.179832407743275</v>
+        <v>1.208575577568379</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.667650585051655</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.814073069324323</v>
+        <v>2.857187824061978</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.152637939876755</v>
+        <v>-3.080780015313996</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.192605314108904</v>
+        <v>1.221348483934008</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.7060342476098062</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834522708201582</v>
+        <v>2.877637462939238</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.975521609841589</v>
+        <v>-2.90366368527883</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.260180874968273</v>
+        <v>1.288924044793376</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.7060342476098062</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831251737046884</v>
+        <v>2.87436649178454</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.020613854675135</v>
+        <v>-2.948755930112376</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.242827368796767</v>
+        <v>1.271570538621871</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5722802798776575</v>
+        <v>0.6441382044404164</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794797502907163</v>
+        <v>2.837912257644819</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.841238433436367</v>
+        <v>-2.769380508873608</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.308364512598689</v>
+        <v>1.337107682423793</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7290570380483762</v>
+        <v>0.800914962611135</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.882650533116009</v>
+        <v>2.925765287853664</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.886252646956974</v>
+        <v>-2.814394722394214</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.271166282522036</v>
+        <v>1.29990945234714</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6987081427337716</v>
+        <v>0.7705660672965304</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845248651258836</v>
+        <v>2.888363405996492</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.153257157229409</v>
+        <v>-3.08139923266665</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.170056040752008</v>
+        <v>1.198799210577111</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5043451046908229</v>
+        <v>0.5762030292535818</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734322390772013</v>
+        <v>2.777437145509668</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.254454938666582</v>
+        <v>-3.182597014103822</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.12878085007364</v>
+        <v>1.157524019898744</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5077942157082627</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692481024541323</v>
+        <v>2.735595779278978</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.247943972052269</v>
+        <v>-3.17608604748951</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.128985198273682</v>
+        <v>1.157728368098786</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5077942157082627</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.690080986095639</v>
+        <v>2.733195740833295</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.228905844344972</v>
+        <v>-3.157047919782213</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.133125168564846</v>
+        <v>1.161868338389949</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4496106043770681</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651695538505167</v>
+        <v>2.694810293242823</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.26003247549559</v>
+        <v>-3.188174550932831</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.298256385043279</v>
+        <v>1.326999554868383</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4496106043770681</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.829277407443848</v>
+        <v>2.872392162181503</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.273899236829507</v>
+        <v>-3.202041312266748</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.293543009495846</v>
+        <v>1.322286179320949</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.4117526876432452</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.807395986389688</v>
+        <v>2.850510741127343</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.229095065289577</v>
+        <v>-3.157237140726818</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.317473208508743</v>
+        <v>1.346216378333847</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.4117526876432452</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.813404516786614</v>
+        <v>2.856519271524269</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.081352095054575</v>
+        <v>-3.009494170491816</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.274520617879944</v>
+        <v>1.303263787705047</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5795600448781284</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.812039152404743</v>
+        <v>2.855153907142399</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.183366777585796</v>
+        <v>-3.111508853023037</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.236508366398936</v>
+        <v>1.26525153622404</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5795600448781284</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814832773936224</v>
+        <v>2.85794752867388</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.177214071533012</v>
+        <v>-3.105356146970252</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239631797211709</v>
+        <v>1.268374967036812</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5138548263681537</v>
+        <v>0.5857127509309127</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.819186745959553</v>
+        <v>2.862301500697209</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.194023369683513</v>
+        <v>-3.122165445120754</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.231988554691618</v>
+        <v>1.260731724516722</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5689034527804111</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.808181643809362</v>
+        <v>2.851296398547018</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.131725370907391</v>
+        <v>-3.059867446344632</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.323243307998888</v>
+        <v>1.351986477823992</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5689034527804111</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.874517197606183</v>
+        <v>2.917631952343839</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.929935173242233</v>
+        <v>-2.858077248679474</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.206251388779078</v>
+        <v>1.234994558604182</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6950637203868064</v>
+        <v>0.7669216449495655</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.795620114621803</v>
+        <v>2.838734869359458</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.765122170163386</v>
+        <v>-2.693264245600627</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.342466822332792</v>
+        <v>1.371209992157896</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8598767234656534</v>
+        <v>0.9317346480284124</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.964798148791286</v>
+        <v>3.007912903528942</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.862862714788361</v>
+        <v>-2.791004790225601</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.317998340598846</v>
+        <v>1.34674151042395</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8439874453326732</v>
+        <v>0.9158453698954323</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.969892318027542</v>
+        <v>3.013007072765197</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.03920047491129</v>
+        <v>-2.967342550348531</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.245999217374346</v>
+        <v>1.27474238719945</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6676496852097438</v>
+        <v>0.7395076097725028</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.862625642778456</v>
+        <v>2.905740397516111</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.962778428479363</v>
+        <v>-2.890920503916604</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.275059653987045</v>
+        <v>1.303802823812149</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6676496852097438</v>
+        <v>0.7395076097725028</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861117260818384</v>
+        <v>2.904232015556039</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.918405296840795</v>
+        <v>-2.846547372278035</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.292671774077909</v>
+        <v>1.321414943903013</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7120228168483124</v>
+        <v>0.7838807414110714</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.887604007236962</v>
+        <v>2.930718761974617</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.795571075953627</v>
+        <v>-2.723713151390868</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.336199256571366</v>
+        <v>1.36494242639647</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7120228168483124</v>
+        <v>0.7838807414110714</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.881997801375552</v>
+        <v>2.925112556113207</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.747915345392571</v>
+        <v>-2.676057420829812</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.361643305823593</v>
+        <v>1.390386475648697</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.759678547409368</v>
+        <v>0.8315364719721271</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.91697299673999</v>
+        <v>2.960087751477646</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.647397186893817</v>
+        <v>-2.575539262331057</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.40674294259782</v>
+        <v>1.435486112422924</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8601967059081226</v>
+        <v>0.9320546304708817</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.982176265213968</v>
+        <v>3.025291019951623</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.708063777296206</v>
+        <v>-2.636205852733446</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.369230978912737</v>
+        <v>1.39797414873784</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7784983891895889</v>
+        <v>0.850356313752348</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.91991194765872</v>
+        <v>2.963026702396375</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.663225375687808</v>
+        <v>-2.591367451125048</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.391264042166724</v>
+        <v>1.420007211991828</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7830418221344584</v>
+        <v>0.8548997466972175</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.92673571003627</v>
+        <v>2.969850464773925</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.763984011444806</v>
+        <v>-2.692126086882047</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.355121527495003</v>
+        <v>1.383864697320107</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.694216253407453</v>
+        <v>0.766074177970212</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.877601308431145</v>
+        <v>2.9207160631688</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.719781174358906</v>
+        <v>-2.647923249796146</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.3786822648572</v>
+        <v>1.407425434682304</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7384190904933534</v>
+        <v>0.8102770150561125</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.910002613210522</v>
+        <v>2.953117367948177</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.756760202022349</v>
+        <v>-2.68490227745959</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.362300654261071</v>
+        <v>1.391043824086174</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7753929922846839</v>
+        <v>0.847250916847443</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.930596954754568</v>
+        <v>2.973711709492223</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.598468784483077</v>
+        <v>-2.526610859920317</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.476864986459819</v>
+        <v>1.505608156284923</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7753929922846839</v>
+        <v>0.847250916847443</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.981844719937608</v>
+        <v>3.024959474675263</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.390826780848601</v>
+        <v>-2.318968856285841</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.558362492507863</v>
+        <v>1.587105662332966</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9830349959191601</v>
+        <v>1.054892920481919</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.104870626712547</v>
+        <v>3.147985381450202</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.339794688126072</v>
+        <v>-2.267936763563313</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.573723557835144</v>
+        <v>1.602466727660248</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.034067088641688</v>
+        <v>1.105925013204447</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.130438110584334</v>
+        <v>3.173552865321989</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.274570506998867</v>
+        <v>-2.202712582436107</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.617000634378731</v>
+        <v>1.645743804203835</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.099291269768894</v>
+        <v>1.171149194331653</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.186760023353362</v>
+        <v>3.229874778091017</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.237143486927733</v>
+        <v>-2.165285562364974</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.627932414706465</v>
+        <v>1.656675584531569</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.104542807798075</v>
+        <v>1.176400732360835</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.185871918470151</v>
+        <v>3.228986673207807</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.257255142962441</v>
+        <v>-2.185397218399682</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.621144544623822</v>
+        <v>1.649887714448926</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.115570152795495</v>
+        <v>1.187428077358254</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.193745117799843</v>
+        <v>3.236859872537499</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.203510328535236</v>
+        <v>-2.131652403972477</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.803200241415915</v>
+        <v>1.831943411241018</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.125633462235957</v>
+        <v>1.197491386798716</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.360340874485331</v>
+        <v>3.403455629222986</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.179718759929094</v>
+        <v>-2.107860835366335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.932829778076189</v>
+        <v>1.961572947901293</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.149425030842099</v>
+        <v>1.221282955404858</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.494728724866834</v>
+        <v>3.537843479604489</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.153634675665286</v>
+        <v>-2.081776751102527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.934971387795571</v>
+        <v>1.963714557620675</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.149425030842099</v>
+        <v>1.221282955404858</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.486436700880692</v>
+        <v>3.529551455618348</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.075503494816339</v>
+        <v>-2.00364557025358</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.964417055718929</v>
+        <v>1.993160225544033</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.223601841725784</v>
+        <v>1.295459766288543</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.529135982994683</v>
+        <v>3.572250737732338</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.066611033423056</v>
+        <v>-1.994753108860297</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.985528446003034</v>
+        <v>2.014271615828138</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.223601841725784</v>
+        <v>1.295459766288543</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.546690388721474</v>
+        <v>3.58980514345913</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.235087150392934</v>
+        <v>-2.163229225830174</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.909993046619667</v>
+        <v>1.938736216444771</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.195654006009203</v>
+        <v>1.267511930571962</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.52177673469611</v>
+        <v>3.564891489433765</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.537287621531351</v>
+        <v>-1.465429696968591</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.170382555352162</v>
+        <v>2.199125725177265</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.125305946638792</v>
+        <v>1.197163871201552</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.460837596261725</v>
+        <v>3.503952350999381</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.514566517848198</v>
+        <v>-1.442708593285439</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.170135019322327</v>
+        <v>2.198878189147431</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.125305946638792</v>
+        <v>1.197163871201552</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.45150161875863</v>
+        <v>3.494616373496285</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.512841474558155</v>
+        <v>-1.440983549995395</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.329731162489514</v>
+        <v>2.358474332314618</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.127030989928836</v>
+        <v>1.198888914491595</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.611442770583825</v>
+        <v>3.654557525321481</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>2.844797629064067</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.439240010641333</v>
+        <v>-1.380278690805491</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.396249570549889</v>
+        <v>2.292329728428123</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.180228278285245</v>
+        <v>1.252202244042504</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.680438966091317</v>
+        <v>3.59611897548957</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>2.841472985053612</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.387804677256674</v>
+        <v>-1.328843357420831</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.413499059893298</v>
+        <v>2.309579217771532</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.231663611669905</v>
+        <v>1.303637577427164</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.707975522111658</v>
+        <v>3.623655531509911</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>2.851479138698354</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.360853452930186</v>
+        <v>-1.301892133094343</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.434285703268634</v>
+        <v>2.330365861146869</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.246543957697624</v>
+        <v>1.318517923454883</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.726909883373031</v>
+        <v>3.642589892771284</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.035582270843313</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.496806460986502</v>
+        <v>-1.437845141150659</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.564007632191068</v>
+        <v>2.460087790069302</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.246543957697624</v>
+        <v>1.318517923454883</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.911013015517991</v>
+        <v>3.826693024916243</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.027698965746306</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.519214578791374</v>
+        <v>-1.460253258955531</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.547161079972112</v>
+        <v>2.443241237850346</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.246543957697624</v>
+        <v>1.318517923454883</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.903129710420984</v>
+        <v>3.818809719819236</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.029752965295943</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.667220346270773</v>
+        <v>-1.608259026434931</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.49001277252999</v>
+        <v>2.386092930408224</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.159816948834082</v>
+        <v>1.231790914591342</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.853147504652496</v>
+        <v>3.768827514050749</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.086006683017791</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.676661272159303</v>
+        <v>-1.61769995232346</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.542490119896425</v>
+        <v>2.438570277774659</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.282244066377474</v>
+        <v>1.354218032134733</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.982857492900378</v>
+        <v>3.89853750229863</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.088897777563091</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.675374508619746</v>
+        <v>-1.616413188783904</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.545895919857549</v>
+        <v>2.441976077735783</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.28353082991703</v>
+        <v>1.35550479567429</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.986520645569413</v>
+        <v>3.902200654967666</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.087009590456867</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.676931562609038</v>
+        <v>-1.617970242773195</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.543384911155607</v>
+        <v>2.439465069033841</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.28353082991703</v>
+        <v>1.35550479567429</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.984632458463188</v>
+        <v>3.900312467861441</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.081829820059729</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.684203448132503</v>
+        <v>-1.62524212829666</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.535296386549084</v>
+        <v>2.431376544427318</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.276258944393565</v>
+        <v>1.348232910150825</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.975089556751971</v>
+        <v>3.890769566150224</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.080263830269881</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.682362429074251</v>
+        <v>-1.623401109238408</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.534466804382537</v>
+        <v>2.43054696226077</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.277527171065034</v>
+        <v>1.349501136822293</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.974284502965005</v>
+        <v>3.889964512363258</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.0933372371358</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.689271134573932</v>
+        <v>-1.630309814738089</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.544776729048583</v>
+        <v>2.440856886926817</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.277527171065034</v>
+        <v>1.349501136822293</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.987357909830924</v>
+        <v>3.903037919229176</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.0933372371358</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.690832777388791</v>
+        <v>-1.631871457552949</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.544152071922639</v>
+        <v>2.440232229800873</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.277527171065034</v>
+        <v>1.349501136822293</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.987357909830924</v>
+        <v>3.903037919229176</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.091861278262802</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.718733564498264</v>
+        <v>-1.659772244662422</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.531515798205852</v>
+        <v>2.427595956084086</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.242930246922099</v>
+        <v>1.314904212679358</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.965123796472165</v>
+        <v>3.880803805870417</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.088625722240001</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.721766562010938</v>
+        <v>-1.662805242175096</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.527067043177981</v>
+        <v>2.423147201056215</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.239897249409425</v>
+        <v>1.311871215166684</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.960068441941759</v>
+        <v>3.875748451340011</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.155331681830504</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.741827883287445</v>
+        <v>-1.682866563451603</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.585748474257882</v>
+        <v>2.481828632136116</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.219835928132918</v>
+        <v>1.291809893890177</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.014737608766358</v>
+        <v>3.930417618164611</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.295643400832351</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.998548701282269</v>
+        <v>-1.939587381446427</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.6233718660618</v>
+        <v>2.519452023940033</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.111421353989103</v>
+        <v>1.183395319746363</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.090000583281917</v>
+        <v>4.00568059268017</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.364623669977991</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.15253511905841</v>
+        <v>-2.093573799222567</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.630757568096983</v>
+        <v>2.526837725975217</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.111421353989103</v>
+        <v>1.183395319746363</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.158980852427557</v>
+        <v>4.074660861825809</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.350674872098112</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.102013215230744</v>
+        <v>-2.043051895394901</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.637017531748171</v>
+        <v>2.533097689626404</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.111421353989103</v>
+        <v>1.183395319746363</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.145032054547677</v>
+        <v>4.06071206394593</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.362545361153526</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.354488369238468</v>
+        <v>-2.295527049402625</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.547897959200495</v>
+        <v>2.443978117078728</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.111421353989103</v>
+        <v>1.183395319746363</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.156902543603092</v>
+        <v>4.072582553001344</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.36375589567247</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.623961171160176</v>
+        <v>-2.564999851324334</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.441319372950755</v>
+        <v>2.337399530828989</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.111421353989103</v>
+        <v>1.183395319746363</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.158113078122035</v>
+        <v>4.073793087520288</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.367877637899791</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.781505242889617</v>
+        <v>-2.722543923053775</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.3824234864863</v>
+        <v>2.278503644364534</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.044519548848829</v>
+        <v>1.116493514606088</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.122093737265192</v>
+        <v>4.037773746663444</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.362955490635981</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.910355793591664</v>
+        <v>-2.851394473755821</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.325961118941671</v>
+        <v>2.222041276819905</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.003526139998107</v>
+        <v>1.075500105755367</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.092575544690948</v>
+        <v>4.008255554089201</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,45 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.867083857469643</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>3.525159547335025</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.027323486230555</v>
+        <v>-3.035684082719162</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.441378098585159</v>
+        <v>2.310529489933613</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.003526139998107</v>
+        <v>1.075500105755367</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.254779601389993</v>
+        <v>4.170459610788245</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="2" t="n">
+        <v>45486</v>
+      </c>
+      <c r="B2024" t="n">
+        <v>3.863984354578389</v>
+      </c>
+      <c r="C2024" t="n">
+        <v>3.671533770919955</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>-3.035684082719162</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>2.310529489933613</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>1.075500105755367</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>3.664597567906323</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.1%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-65.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.9%</t>
+          <t>457.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-465.1%</t>
+          <t>-479.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.2%</t>
+          <t>-138.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.7%</t>
+          <t>-132.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-116.4%</t>
+          <t>-132.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-81.0%</t>
         </is>
       </c>
     </row>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.659631352661576</v>
+        <v>-3.585270518981897</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.515252905148068</v>
+        <v>1.54499723861994</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2764219364157369</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.539458269297077</v>
+        <v>-3.465097435617398</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.56446798293417</v>
+        <v>1.594212316406041</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3965950197802359</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.394786124197339</v>
+        <v>-3.320425290517661</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.632424943535504</v>
+        <v>1.662169277007376</v>
       </c>
       <c r="F1932" t="n">
         <v>0.5412671648799733</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.454660951555032</v>
+        <v>-3.380300117875353</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.594512503993853</v>
+        <v>1.624256837465725</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4813923375222812</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.334840720644194</v>
+        <v>-3.260479886964516</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.657729765592397</v>
+        <v>1.687474099064268</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4813923375222812</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.337310427106</v>
+        <v>-3.262949593426322</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.564386082330116</v>
+        <v>1.594130415801987</v>
       </c>
       <c r="F1935" t="n">
         <v>0.478922631060475</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.40568061343001</v>
+        <v>-3.331319779750332</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.456299869285814</v>
+        <v>1.486044202757685</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4881983300966899</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.419468666277057</v>
+        <v>-3.345107832597378</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.441221356778886</v>
+        <v>1.470965690250758</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4881983300966899</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.450461825605762</v>
+        <v>-3.376100991926084</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.253533658087791</v>
+        <v>1.283277991559662</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4881983300966899</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.274987565813293</v>
+        <v>-3.200626732133614</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.328290593996566</v>
+        <v>1.358034927468438</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4881983300966899</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.385923818454541</v>
+        <v>-3.311562984774863</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.259658121701274</v>
+        <v>1.289402455173145</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4881983300966899</v>
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.280402348419501</v>
+        <v>-3.277899439302581</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.23040502311674</v>
+        <v>1.231406186763508</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.899154266877326</v>
+        <v>2.856039512139671</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.220549729215778</v>
+        <v>-3.218046820098858</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.264518457230362</v>
+        <v>1.26551962087713</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.909326653309459</v>
+        <v>2.866211898571803</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.1343062661894</v>
+        <v>-3.131803357072481</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.293962113014773</v>
+        <v>1.294963276661541</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5937198001317308</v>
+        <v>0.5218618755689718</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.904272923883319</v>
+        <v>2.861158169145663</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.17961308558838</v>
+        <v>-3.17711017647146</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.267615160699707</v>
+        <v>1.268616324346474</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5529096371225</v>
+        <v>0.481051712559741</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.871562601522306</v>
+        <v>2.828447846784651</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.208646190290681</v>
+        <v>-3.206143281173762</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.256553791851887</v>
+        <v>1.257554955498655</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5529096371225</v>
+        <v>0.481051712559741</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.872114474555408</v>
+        <v>2.828999719817752</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.115835708839822</v>
+        <v>-3.113332799722903</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.222950676323597</v>
+        <v>1.223951839970365</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6457201185733593</v>
+        <v>0.5738621940106003</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.857073455317289</v>
+        <v>2.813958700579633</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.16022517816925</v>
+        <v>-3.15772226905233</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.207068364516427</v>
+        <v>1.208069528163194</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6013306492439316</v>
+        <v>0.5294727246811727</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.832313249644233</v>
+        <v>2.789198494906578</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.047553959932999</v>
+        <v>-3.04505105081608</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.24721256032265</v>
+        <v>1.248213723969418</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7140018674801818</v>
+        <v>0.6421439429174229</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.894991689097706</v>
+        <v>2.851876934360051</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.935176958750327</v>
+        <v>-2.932674049633408</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.297654656626386</v>
+        <v>1.298655820273154</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7140018674801818</v>
+        <v>0.6421439429174229</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.900482984928373</v>
+        <v>2.857368230190718</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.96295735665168</v>
+        <v>-2.960454447534761</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.298039699234384</v>
+        <v>1.299040862881152</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6862214695788287</v>
+        <v>0.6143635450160698</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.895311947956101</v>
+        <v>2.852197193218445</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.045958637676959</v>
+        <v>-3.04345572856004</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.103194906824926</v>
+        <v>1.104196070471693</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.72252513724045</v>
+        <v>2.679410382502794</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.15457271612029</v>
+        <v>-3.152069807003371</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.179898936166799</v>
+        <v>1.180900099813566</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.842674797959655</v>
+        <v>2.799560043222</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.119163677872147</v>
+        <v>-3.116660768755228</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.208575577568379</v>
+        <v>1.209576741215147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.667650585051655</v>
+        <v>0.5957926604888961</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.857187824061978</v>
+        <v>2.814073069324323</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.080780015313996</v>
+        <v>-3.078277106197077</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.221348483934008</v>
+        <v>1.222349647580776</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7060342476098062</v>
+        <v>0.6341763230470473</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.877637462939238</v>
+        <v>2.834522708201582</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.90366368527883</v>
+        <v>-2.901160776161911</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.288924044793376</v>
+        <v>1.289925208440144</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7060342476098062</v>
+        <v>0.6341763230470473</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.87436649178454</v>
+        <v>2.831251737046884</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.948755930112376</v>
+        <v>-2.946253020995456</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.271570538621871</v>
+        <v>1.272571702268639</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6441382044404164</v>
+        <v>0.5722802798776575</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.837912257644819</v>
+        <v>2.794797502907163</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.769380508873608</v>
+        <v>-2.766877599756689</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.337107682423793</v>
+        <v>1.33810884607056</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.800914962611135</v>
+        <v>0.7290570380483762</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.925765287853664</v>
+        <v>2.882650533116009</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.814394722394214</v>
+        <v>-2.811891813277295</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.29990945234714</v>
+        <v>1.300910615993908</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7705660672965304</v>
+        <v>0.6987081427337716</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.888363405996492</v>
+        <v>2.845248651258836</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.08139923266665</v>
+        <v>-3.07889632354973</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.198799210577111</v>
+        <v>1.199800374223879</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5762030292535818</v>
+        <v>0.5043451046908229</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.777437145509668</v>
+        <v>2.734322390772013</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.182597014103822</v>
+        <v>-3.180094104986903</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.157524019898744</v>
+        <v>1.158525183545511</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5077942157082627</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.735595779278978</v>
+        <v>2.692481024541323</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.17608604748951</v>
+        <v>-3.173583138372591</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.157728368098786</v>
+        <v>1.158729531745553</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5077942157082627</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.733195740833295</v>
+        <v>2.690080986095639</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.157047919782213</v>
+        <v>-3.154545010665293</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.161868338389949</v>
+        <v>1.162869502036717</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4496106043770681</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.694810293242823</v>
+        <v>2.651695538505167</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.188174550932831</v>
+        <v>-3.185671641815911</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.326999554868383</v>
+        <v>1.32800071851515</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4496106043770681</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.872392162181503</v>
+        <v>2.829277407443848</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.202041312266748</v>
+        <v>-3.199538403149829</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.322286179320949</v>
+        <v>1.323287342967717</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4117526876432452</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850510741127343</v>
+        <v>2.807395986389688</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.157237140726818</v>
+        <v>-3.154734231609899</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.346216378333847</v>
+        <v>1.347217541980615</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4117526876432452</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856519271524269</v>
+        <v>2.813404516786614</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.009494170491816</v>
+        <v>-3.006991261374897</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.303263787705047</v>
+        <v>1.304264951351815</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5795600448781284</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855153907142399</v>
+        <v>2.812039152404743</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.111508853023037</v>
+        <v>-3.109005943906118</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.26525153622404</v>
+        <v>1.266252699870808</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5795600448781284</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.85794752867388</v>
+        <v>2.814832773936224</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.105356146970252</v>
+        <v>-3.102853237853333</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.268374967036812</v>
+        <v>1.26937613068358</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5857127509309127</v>
+        <v>0.5138548263681537</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862301500697209</v>
+        <v>2.819186745959553</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.122165445120754</v>
+        <v>-3.119662536003835</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.260731724516722</v>
+        <v>1.26173288816349</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5689034527804111</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851296398547018</v>
+        <v>2.808181643809362</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.059867446344632</v>
+        <v>-3.057364537227713</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.351986477823992</v>
+        <v>1.352987641470759</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5689034527804111</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.917631952343839</v>
+        <v>2.874517197606183</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.858077248679474</v>
+        <v>-2.855574339562555</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.234994558604182</v>
+        <v>1.235995722250949</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7669216449495655</v>
+        <v>0.6950637203868064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.838734869359458</v>
+        <v>2.795620114621803</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.693264245600627</v>
+        <v>-2.690761336483708</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.371209992157896</v>
+        <v>1.372211155804664</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9317346480284124</v>
+        <v>0.8598767234656534</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.007912903528942</v>
+        <v>2.964798148791286</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.791004790225601</v>
+        <v>-2.788501881108682</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.34674151042395</v>
+        <v>1.347742674070717</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9158453698954323</v>
+        <v>0.8439874453326732</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.013007072765197</v>
+        <v>2.969892318027542</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.967342550348531</v>
+        <v>-2.964839641231611</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.27474238719945</v>
+        <v>1.275743550846217</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7395076097725028</v>
+        <v>0.6676496852097438</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.905740397516111</v>
+        <v>2.862625642778456</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.890920503916604</v>
+        <v>-2.888417594799685</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.303802823812149</v>
+        <v>1.304803987458917</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7395076097725028</v>
+        <v>0.6676496852097438</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.904232015556039</v>
+        <v>2.861117260818384</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.846547372278035</v>
+        <v>-2.844044463161116</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.321414943903013</v>
+        <v>1.32241610754978</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7838807414110714</v>
+        <v>0.7120228168483124</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.930718761974617</v>
+        <v>2.887604007236962</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.723713151390868</v>
+        <v>-2.721210242273949</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.36494242639647</v>
+        <v>1.365943590043238</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7838807414110714</v>
+        <v>0.7120228168483124</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.925112556113207</v>
+        <v>2.881997801375552</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.676057420829812</v>
+        <v>-2.673554511712893</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.390386475648697</v>
+        <v>1.391387639295465</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8315364719721271</v>
+        <v>0.759678547409368</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.960087751477646</v>
+        <v>2.91697299673999</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.575539262331057</v>
+        <v>-2.573036353214138</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.435486112422924</v>
+        <v>1.436487276069691</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9320546304708817</v>
+        <v>0.8601967059081226</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.025291019951623</v>
+        <v>2.982176265213968</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.636205852733446</v>
+        <v>-2.633702943616527</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.39797414873784</v>
+        <v>1.398975312384608</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.850356313752348</v>
+        <v>0.7784983891895889</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.963026702396375</v>
+        <v>2.91991194765872</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.591367451125048</v>
+        <v>-2.588864542008129</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.420007211991828</v>
+        <v>1.421008375638596</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8548997466972175</v>
+        <v>0.7830418221344584</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.969850464773925</v>
+        <v>2.92673571003627</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.692126086882047</v>
+        <v>-2.689623177765128</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.383864697320107</v>
+        <v>1.384865860966874</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.766074177970212</v>
+        <v>0.694216253407453</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.9207160631688</v>
+        <v>2.877601308431145</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.647923249796146</v>
+        <v>-2.645420340679227</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.407425434682304</v>
+        <v>1.408426598329072</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8102770150561125</v>
+        <v>0.7384190904933534</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.953117367948177</v>
+        <v>2.910002613210522</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.68490227745959</v>
+        <v>-2.68239936834267</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.391043824086174</v>
+        <v>1.392044987732942</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.847250916847443</v>
+        <v>0.7753929922846839</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.973711709492223</v>
+        <v>2.930596954754568</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.526610859920317</v>
+        <v>-2.524107950803398</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.505608156284923</v>
+        <v>1.506609319931691</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.847250916847443</v>
+        <v>0.7753929922846839</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.024959474675263</v>
+        <v>2.981844719937608</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.318968856285841</v>
+        <v>-2.316465947168922</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.587105662332966</v>
+        <v>1.588106825979734</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.054892920481919</v>
+        <v>0.9830349959191601</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.147985381450202</v>
+        <v>3.104870626712547</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.267936763563313</v>
+        <v>-2.265433854446394</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.602466727660248</v>
+        <v>1.603467891307016</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.105925013204447</v>
+        <v>1.034067088641688</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.173552865321989</v>
+        <v>3.130438110584334</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.202712582436107</v>
+        <v>-2.200209673319188</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.645743804203835</v>
+        <v>1.646744967850603</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.171149194331653</v>
+        <v>1.099291269768894</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.229874778091017</v>
+        <v>3.186760023353362</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.165285562364974</v>
+        <v>-2.162782653248054</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.656675584531569</v>
+        <v>1.657676748178337</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.176400732360835</v>
+        <v>1.104542807798075</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.228986673207807</v>
+        <v>3.185871918470151</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.185397218399682</v>
+        <v>-2.182894309282763</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.649887714448926</v>
+        <v>1.650888878095694</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.187428077358254</v>
+        <v>1.115570152795495</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.236859872537499</v>
+        <v>3.193745117799843</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.131652403972477</v>
+        <v>-2.129149494855558</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.831943411241018</v>
+        <v>1.832944574887786</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.197491386798716</v>
+        <v>1.125633462235957</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.403455629222986</v>
+        <v>3.360340874485331</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.107860835366335</v>
+        <v>-2.105357926249416</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.961572947901293</v>
+        <v>1.962574111548061</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.221282955404858</v>
+        <v>1.149425030842099</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.537843479604489</v>
+        <v>3.494728724866834</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.081776751102527</v>
+        <v>-2.079273841985608</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.963714557620675</v>
+        <v>1.964715721267443</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.221282955404858</v>
+        <v>1.149425030842099</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.529551455618348</v>
+        <v>3.486436700880692</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.00364557025358</v>
+        <v>-2.001142661136661</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.993160225544033</v>
+        <v>1.994161389190801</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.295459766288543</v>
+        <v>1.223601841725784</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.572250737732338</v>
+        <v>3.529135982994683</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.994753108860297</v>
+        <v>-1.992250199743377</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.014271615828138</v>
+        <v>2.015272779474905</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.295459766288543</v>
+        <v>1.223601841725784</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.58980514345913</v>
+        <v>3.546690388721474</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.163229225830174</v>
+        <v>-2.160726316713255</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.938736216444771</v>
+        <v>1.939737380091538</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.267511930571962</v>
+        <v>1.195654006009203</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.564891489433765</v>
+        <v>3.52177673469611</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.465429696968591</v>
+        <v>-1.462926787851672</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.199125725177265</v>
+        <v>2.200126888824033</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.197163871201552</v>
+        <v>1.125305946638792</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.503952350999381</v>
+        <v>3.460837596261725</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.442708593285439</v>
+        <v>-1.440205684168519</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.198878189147431</v>
+        <v>2.199879352794199</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.197163871201552</v>
+        <v>1.125305946638792</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.494616373496285</v>
+        <v>3.45150161875863</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.440983549995395</v>
+        <v>-1.438480640878476</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.358474332314618</v>
+        <v>2.359475495961386</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.198888914491595</v>
+        <v>1.127030989928836</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.654557525321481</v>
+        <v>3.611442770583825</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.844797629064067</v>
+        <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.380278690805491</v>
+        <v>-1.593261647656731</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.292329728428123</v>
+        <v>2.33464091574373</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.252202244042504</v>
+        <v>1.09366331587436</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.59611897548957</v>
+        <v>3.628499988644786</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.841472985053612</v>
+        <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.328843357420831</v>
+        <v>-1.541826314272071</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.309579217771532</v>
+        <v>2.351890405087139</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.303637577427164</v>
+        <v>1.145098649259019</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.623655531509911</v>
+        <v>3.656036544665127</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.851479138698354</v>
+        <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.301892133094343</v>
+        <v>-1.514875089945583</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.330365861146869</v>
+        <v>2.372677048462475</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.318517923454883</v>
+        <v>1.159978995286739</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.642589892771284</v>
+        <v>3.6749709059265</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.035582270843313</v>
+        <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.437845141150659</v>
+        <v>-1.650828098001899</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.460087790069302</v>
+        <v>2.502398977384909</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.318517923454883</v>
+        <v>1.159978995286739</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.826693024916243</v>
+        <v>3.859074038071459</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.027698965746306</v>
+        <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.460253258955531</v>
+        <v>-1.673236215806772</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.443241237850346</v>
+        <v>2.485552425165953</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.318517923454883</v>
+        <v>1.159978995286739</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.818809719819236</v>
+        <v>3.851190732974453</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.029752965295943</v>
+        <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.608259026434931</v>
+        <v>-1.821241983286171</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.386092930408224</v>
+        <v>2.428404117723831</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.231790914591342</v>
+        <v>1.073251986423197</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.768827514050749</v>
+        <v>3.801208527205965</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.086006683017791</v>
+        <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.61769995232346</v>
+        <v>-1.830682909174701</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.438570277774659</v>
+        <v>2.480881465090266</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.354218032134733</v>
+        <v>1.195679103966588</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.89853750229863</v>
+        <v>3.930918515453847</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.088897777563091</v>
+        <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.616413188783904</v>
+        <v>-1.829396145635144</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.441976077735783</v>
+        <v>2.48428726505139</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.35550479567429</v>
+        <v>1.196965867506145</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.902200654967666</v>
+        <v>3.934581668122882</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.087009590456867</v>
+        <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.617970242773195</v>
+        <v>-1.830953199624435</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.439465069033841</v>
+        <v>2.481776256349448</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.35550479567429</v>
+        <v>1.196965867506145</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.900312467861441</v>
+        <v>3.932693481016657</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.081829820059729</v>
+        <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.62524212829666</v>
+        <v>-1.8382250851479</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.431376544427318</v>
+        <v>2.473687731742925</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.348232910150825</v>
+        <v>1.18969398198268</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.890769566150224</v>
+        <v>3.923150579305441</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.080263830269881</v>
+        <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.623401109238408</v>
+        <v>-1.836384066089649</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.43054696226077</v>
+        <v>2.472858149576378</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.349501136822293</v>
+        <v>1.190962208654148</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.889964512363258</v>
+        <v>3.922345525518474</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.0933372371358</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.630309814738089</v>
+        <v>-1.843292771589329</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.440856886926817</v>
+        <v>2.483168074242424</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.349501136822293</v>
+        <v>1.190962208654148</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.903037919229176</v>
+        <v>3.935418932384392</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.0933372371358</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.631871457552949</v>
+        <v>-1.844854414404189</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.440232229800873</v>
+        <v>2.48254341711648</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.349501136822293</v>
+        <v>1.190962208654148</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903037919229176</v>
+        <v>3.935418932384392</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.091861278262802</v>
+        <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.659772244662422</v>
+        <v>-1.872755201513662</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.427595956084086</v>
+        <v>2.469907143399693</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.314904212679358</v>
+        <v>1.156365284511214</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.880803805870417</v>
+        <v>3.913184819025633</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.088625722240001</v>
+        <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.662805242175096</v>
+        <v>-1.875788199026336</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.423147201056215</v>
+        <v>2.465458388371822</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.311871215166684</v>
+        <v>1.15333228699854</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.875748451340011</v>
+        <v>3.908129464495228</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.155331681830504</v>
+        <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.682866563451603</v>
+        <v>-1.895849520302843</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.481828632136116</v>
+        <v>2.524139819451723</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.291809893890177</v>
+        <v>1.133270965722033</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.930417618164611</v>
+        <v>3.962798631319828</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.295643400832351</v>
+        <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.939587381446427</v>
+        <v>-2.152570338297667</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.519452023940033</v>
+        <v>2.561763211255641</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.183395319746363</v>
+        <v>1.024856391578218</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.00568059268017</v>
+        <v>4.038061605835385</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.364623669977991</v>
+        <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.093573799222567</v>
+        <v>-2.306556756073807</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.526837725975217</v>
+        <v>2.569148913290824</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.183395319746363</v>
+        <v>1.024856391578218</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.074660861825809</v>
+        <v>4.107041874981025</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.350674872098112</v>
+        <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.043051895394901</v>
+        <v>-2.256034852246141</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.533097689626404</v>
+        <v>2.575408876942011</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.183395319746363</v>
+        <v>1.024856391578218</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.06071206394593</v>
+        <v>4.093093077101146</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.362545361153526</v>
+        <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.295527049402625</v>
+        <v>-2.508510006253866</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.443978117078728</v>
+        <v>2.486289304394336</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.183395319746363</v>
+        <v>1.024856391578218</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.072582553001344</v>
+        <v>4.10496356615656</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.36375589567247</v>
+        <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.564999851324334</v>
+        <v>-2.777982808175574</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.337399530828989</v>
+        <v>2.379710718144596</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.183395319746363</v>
+        <v>1.024856391578218</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.073793087520288</v>
+        <v>4.106174100675504</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.367877637899791</v>
+        <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.722543923053775</v>
+        <v>-2.935526879905015</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.278503644364534</v>
+        <v>2.320814831680141</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.116493514606088</v>
+        <v>0.9579545864379435</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.037773746663444</v>
+        <v>4.070154759818661</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.362955490635981</v>
+        <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.851394473755821</v>
+        <v>-3.064377430607061</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.222041276819905</v>
+        <v>2.264352464135512</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.075500105755367</v>
+        <v>0.916961177587222</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.008255554089201</v>
+        <v>4.040636567244417</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215466</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.525159547335025</v>
+        <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.035684082719162</v>
+        <v>-3.181345123245952</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.310529489933613</v>
+        <v>2.379769443779</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.075500105755367</v>
+        <v>0.916961177587222</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.170459610788245</v>
+        <v>4.202840623943461</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.863984354578389</v>
+        <v>3.758957890400163</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.671533770919955</v>
+        <v>3.656805233478649</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.035684082719162</v>
+        <v>-3.181345123245952</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.310529489933613</v>
+        <v>2.379769443779</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.075500105755367</v>
+        <v>0.916961177587222</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.664597567906323</v>
+        <v>3.649869030465017</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>121.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.8%</t>
+          <t>-63.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.9%</t>
+          <t>458.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-479.7%</t>
+          <t>-444.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-138.2%</t>
+          <t>-124.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-130.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-132.3%</t>
+          <t>-95.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.585270518981897</v>
+        <v>-3.659631352661576</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.54499723861994</v>
+        <v>1.515252905148068</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2764219364157369</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.465097435617398</v>
+        <v>-3.539458269297077</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.594212316406041</v>
+        <v>1.56446798293417</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3965950197802359</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.320425290517661</v>
+        <v>-3.394786124197339</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.662169277007376</v>
+        <v>1.632424943535504</v>
       </c>
       <c r="F1932" t="n">
         <v>0.5412671648799733</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.380300117875353</v>
+        <v>-3.454660951555032</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.624256837465725</v>
+        <v>1.594512503993853</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4813923375222812</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.260479886964516</v>
+        <v>-3.334840720644194</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.687474099064268</v>
+        <v>1.657729765592397</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4813923375222812</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.262949593426322</v>
+        <v>-3.337310427106</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.594130415801987</v>
+        <v>1.564386082330116</v>
       </c>
       <c r="F1935" t="n">
         <v>0.478922631060475</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.331319779750332</v>
+        <v>-3.40568061343001</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.486044202757685</v>
+        <v>1.456299869285814</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4881983300966899</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.345107832597378</v>
+        <v>-3.419468666277057</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.470965690250758</v>
+        <v>1.441221356778886</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4881983300966899</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.376100991926084</v>
+        <v>-3.450461825605762</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.283277991559662</v>
+        <v>1.253533658087791</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4881983300966899</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.200626732133614</v>
+        <v>-3.274987565813293</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.358034927468438</v>
+        <v>1.328290593996566</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4881983300966899</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.311562984774863</v>
+        <v>-3.385923818454541</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.289402455173145</v>
+        <v>1.259658121701274</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4881983300966899</v>
@@ -46194,10 +46194,10 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.277899439302581</v>
+        <v>-3.35226027298226</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.231406186763508</v>
+        <v>1.201661853291636</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5218618755689718</v>
@@ -46217,10 +46217,10 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.218046820098858</v>
+        <v>-3.292407653778537</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.26551962087713</v>
+        <v>1.235775287405258</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5218618755689718</v>
@@ -46240,10 +46240,10 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.131803357072481</v>
+        <v>-3.206164190752159</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.294963276661541</v>
+        <v>1.265218943189669</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5218618755689718</v>
@@ -46263,10 +46263,10 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.17711017647146</v>
+        <v>-3.251471010151139</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.268616324346474</v>
+        <v>1.238871990874603</v>
       </c>
       <c r="F1944" t="n">
         <v>0.481051712559741</v>
@@ -46286,10 +46286,10 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.206143281173762</v>
+        <v>-3.280504114853441</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.257554955498655</v>
+        <v>1.227810622026784</v>
       </c>
       <c r="F1945" t="n">
         <v>0.481051712559741</v>
@@ -46309,10 +46309,10 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.113332799722903</v>
+        <v>-3.187693633402581</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.223951839970365</v>
+        <v>1.194207506498493</v>
       </c>
       <c r="F1946" t="n">
         <v>0.5738621940106003</v>
@@ -46332,10 +46332,10 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.15772226905233</v>
+        <v>-3.232083102732009</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.208069528163194</v>
+        <v>1.178325194691323</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5294727246811727</v>
@@ -46355,10 +46355,10 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.04505105081608</v>
+        <v>-3.119411884495759</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.248213723969418</v>
+        <v>1.218469390497546</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6421439429174229</v>
@@ -46378,10 +46378,10 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.932674049633408</v>
+        <v>-3.007034883313086</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.298655820273154</v>
+        <v>1.268911486801282</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6421439429174229</v>
@@ -46401,10 +46401,10 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.960454447534761</v>
+        <v>-3.034815281214439</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.299040862881152</v>
+        <v>1.26929652940928</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6143635450160698</v>
@@ -46424,10 +46424,10 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.04345572856004</v>
+        <v>-3.117816562239718</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.104196070471693</v>
+        <v>1.074451736999822</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5957926604888961</v>
@@ -46447,10 +46447,10 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.152069807003371</v>
+        <v>-3.226430640683049</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.180900099813566</v>
+        <v>1.151155766341695</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5957926604888961</v>
@@ -46470,10 +46470,10 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.116660768755228</v>
+        <v>-3.191021602434907</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.209576741215147</v>
+        <v>1.179832407743275</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5957926604888961</v>
@@ -46493,10 +46493,10 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.078277106197077</v>
+        <v>-3.152637939876755</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.222349647580776</v>
+        <v>1.192605314108904</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6341763230470473</v>
@@ -46516,10 +46516,10 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.901160776161911</v>
+        <v>-2.975521609841589</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.289925208440144</v>
+        <v>1.260180874968273</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6341763230470473</v>
@@ -46539,10 +46539,10 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.946253020995456</v>
+        <v>-3.020613854675135</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.272571702268639</v>
+        <v>1.242827368796767</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5722802798776575</v>
@@ -46562,10 +46562,10 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.766877599756689</v>
+        <v>-2.841238433436367</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.33810884607056</v>
+        <v>1.308364512598689</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7290570380483762</v>
@@ -46585,10 +46585,10 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.811891813277295</v>
+        <v>-2.886252646956974</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.300910615993908</v>
+        <v>1.271166282522036</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6987081427337716</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.07889632354973</v>
+        <v>-3.153257157229409</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.199800374223879</v>
+        <v>1.170056040752008</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5043451046908229</v>
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.180094104986903</v>
+        <v>-3.105346017169412</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.158525183545511</v>
+        <v>1.188424418672508</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5275347021225815</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692481024541323</v>
+        <v>2.747440071127569</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.173583138372591</v>
+        <v>-3.0988350505551</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.158729531745553</v>
+        <v>1.188628766872549</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.5275347021225815</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.690080986095639</v>
+        <v>2.745040032681886</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.154545010665293</v>
+        <v>-3.079796922847803</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.162869502036717</v>
+        <v>1.192768737163713</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4693510907913869</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651695538505167</v>
+        <v>2.706654585091414</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.185671641815911</v>
+        <v>-3.110923553998421</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.32800071851515</v>
+        <v>1.357899953642147</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.4693510907913869</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.829277407443848</v>
+        <v>2.884236454030094</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.199538403149829</v>
+        <v>-3.124790315332338</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.323287342967717</v>
+        <v>1.353186578094713</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.431493174057564</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.807395986389688</v>
+        <v>2.862355032975934</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.154734231609899</v>
+        <v>-3.079986143792408</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.347217541980615</v>
+        <v>1.377116777107611</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.431493174057564</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.813404516786614</v>
+        <v>2.86836356337286</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.006991261374897</v>
+        <v>-2.932243173557406</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.304264951351815</v>
+        <v>1.334164186478812</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5993005312924471</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.812039152404743</v>
+        <v>2.86699819899099</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.109005943906118</v>
+        <v>-3.034257856088627</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.266252699870808</v>
+        <v>1.296151934997804</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.5993005312924471</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814832773936224</v>
+        <v>2.869791820522471</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.102853237853333</v>
+        <v>-3.028105150035842</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.26937613068358</v>
+        <v>1.299275365810576</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5138548263681537</v>
+        <v>0.6054532373452314</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.819186745959553</v>
+        <v>2.8741457925458</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.119662536003835</v>
+        <v>-3.044914448186344</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.26173288816349</v>
+        <v>1.291632123290486</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5886439391947298</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.808181643809362</v>
+        <v>2.863140690395609</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.057364537227713</v>
+        <v>-2.982616449410222</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.352987641470759</v>
+        <v>1.382886876597756</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.497045528217652</v>
+        <v>0.5886439391947298</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.874517197606183</v>
+        <v>2.92947624419243</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.855574339562555</v>
+        <v>-2.780826251745064</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.235995722250949</v>
+        <v>1.265894957377946</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6950637203868064</v>
+        <v>0.7866621313638842</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.795620114621803</v>
+        <v>2.850579161208049</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.690761336483708</v>
+        <v>-2.616013248666217</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.372211155804664</v>
+        <v>1.40211039093166</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8598767234656534</v>
+        <v>0.9514751344427311</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.964798148791286</v>
+        <v>3.019757195377533</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.788501881108682</v>
+        <v>-2.713753793291191</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.347742674070717</v>
+        <v>1.377641909197714</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8439874453326732</v>
+        <v>0.935585856309751</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.969892318027542</v>
+        <v>3.024851364613788</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.964839641231611</v>
+        <v>-2.616539182373526</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.275743550846217</v>
+        <v>1.415063734389452</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6676496852097438</v>
+        <v>1.032800467227417</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.862625642778456</v>
+        <v>3.081716111989059</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.888417594799685</v>
+        <v>-2.540117135941599</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.304803987458917</v>
+        <v>1.444124171002151</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6676496852097438</v>
+        <v>1.032800467227417</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861117260818384</v>
+        <v>3.080207730028988</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.844044463161116</v>
+        <v>-2.495744004303031</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.32241610754978</v>
+        <v>1.461736291093015</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7120228168483124</v>
+        <v>1.077173598865985</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.887604007236962</v>
+        <v>3.106694476447565</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.721210242273949</v>
+        <v>-2.372909783415863</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.365943590043238</v>
+        <v>1.505263773586472</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7120228168483124</v>
+        <v>1.077173598865985</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.881997801375552</v>
+        <v>3.101088270586156</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.673554511712893</v>
+        <v>-2.325254052854808</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.391387639295465</v>
+        <v>1.530707822838699</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.759678547409368</v>
+        <v>1.124829329427041</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.91697299673999</v>
+        <v>3.136063465950594</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.573036353214138</v>
+        <v>-2.224735894356053</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.436487276069691</v>
+        <v>1.575807459612925</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8601967059081226</v>
+        <v>1.225347487925796</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.982176265213968</v>
+        <v>3.201266734424571</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.633702943616527</v>
+        <v>-2.285402484758442</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.398975312384608</v>
+        <v>1.538295495927842</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7784983891895889</v>
+        <v>1.143649171207262</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.91991194765872</v>
+        <v>3.139002416869324</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.588864542008129</v>
+        <v>-2.240564083150044</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.421008375638596</v>
+        <v>1.56032855918183</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7830418221344584</v>
+        <v>1.148192604152131</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.92673571003627</v>
+        <v>3.145826179246874</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.689623177765128</v>
+        <v>-2.341322718907043</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.384865860966874</v>
+        <v>1.524186044510108</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.694216253407453</v>
+        <v>1.059367035425126</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.877601308431145</v>
+        <v>3.096691777641749</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.645420340679227</v>
+        <v>-2.297119881821142</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.408426598329072</v>
+        <v>1.547746781872306</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7384190904933534</v>
+        <v>1.103569872511026</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.910002613210522</v>
+        <v>3.129093082421126</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.68239936834267</v>
+        <v>-2.334098909484585</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.392044987732942</v>
+        <v>1.531365171276176</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7753929922846839</v>
+        <v>1.140543774302357</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.930596954754568</v>
+        <v>3.149687423965172</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.524107950803398</v>
+        <v>-2.175807491945313</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.506609319931691</v>
+        <v>1.645929503474925</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7753929922846839</v>
+        <v>1.140543774302357</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.981844719937608</v>
+        <v>3.200935189148212</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.316465947168922</v>
+        <v>-1.968165488310837</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.588106825979734</v>
+        <v>1.727427009522968</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9830349959191601</v>
+        <v>1.348185777936833</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.104870626712547</v>
+        <v>3.32396109592315</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.265433854446394</v>
+        <v>-1.917133395588309</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.603467891307016</v>
+        <v>1.74278807485025</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.034067088641688</v>
+        <v>1.399217870659361</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.130438110584334</v>
+        <v>3.349528579794937</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.200209673319188</v>
+        <v>-1.851909214461103</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.646744967850603</v>
+        <v>1.786065151393837</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.099291269768894</v>
+        <v>1.464442051786567</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.186760023353362</v>
+        <v>3.405850492563966</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.162782653248054</v>
+        <v>-1.81448219438997</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.657676748178337</v>
+        <v>1.796996931721571</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.104542807798075</v>
+        <v>1.469693589815749</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.185871918470151</v>
+        <v>3.404962387680755</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.182894309282763</v>
+        <v>-1.834593850424678</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.650888878095694</v>
+        <v>1.790209061638928</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.115570152795495</v>
+        <v>1.480720934813168</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.193745117799843</v>
+        <v>3.412835587010447</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.129149494855558</v>
+        <v>-1.780849035997473</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.832944574887786</v>
+        <v>1.97226475843102</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.125633462235957</v>
+        <v>1.49078424425363</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.360340874485331</v>
+        <v>3.579431343695935</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.105357926249416</v>
+        <v>-1.757057467391331</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.962574111548061</v>
+        <v>2.101894295091294</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.149425030842099</v>
+        <v>1.514575812859772</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.494728724866834</v>
+        <v>3.713819194077437</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.079273841985608</v>
+        <v>-1.730973383127523</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.964715721267443</v>
+        <v>2.104035904810677</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.149425030842099</v>
+        <v>1.514575812859772</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.486436700880692</v>
+        <v>3.705527170091296</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.001142661136661</v>
+        <v>-1.652842202278576</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.994161389190801</v>
+        <v>2.133481572734035</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.223601841725784</v>
+        <v>1.588752623743457</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.529135982994683</v>
+        <v>3.748226452205286</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.992250199743377</v>
+        <v>-1.643949740885293</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.015272779474905</v>
+        <v>2.154592963018139</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.223601841725784</v>
+        <v>1.588752623743457</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.546690388721474</v>
+        <v>3.765780857932078</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.160726316713255</v>
+        <v>-1.812425857855171</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.939737380091538</v>
+        <v>2.079057563634772</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.195654006009203</v>
+        <v>1.560804788026876</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.52177673469611</v>
+        <v>3.740867203906713</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.462926787851672</v>
+        <v>-1.114626328993587</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.200126888824033</v>
+        <v>2.339447072367267</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.125305946638792</v>
+        <v>1.490456728656465</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.460837596261725</v>
+        <v>3.679928065472329</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.440205684168519</v>
+        <v>-1.091905225310435</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.199879352794199</v>
+        <v>2.339199536337433</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.125305946638792</v>
+        <v>1.490456728656465</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.45150161875863</v>
+        <v>3.670592087969233</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.438480640878476</v>
+        <v>-1.090180182020391</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.359475495961386</v>
+        <v>2.498795679504619</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.127030989928836</v>
+        <v>1.492181771946509</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.611442770583825</v>
+        <v>3.830533239794429</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.593261647656731</v>
+        <v>-1.244961188798646</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.33464091574373</v>
+        <v>2.473961099286964</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.09366331587436</v>
+        <v>1.458814097892033</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.628499988644786</v>
+        <v>3.847590457855389</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.541826314272071</v>
+        <v>-1.193525855413987</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.351890405087139</v>
+        <v>2.491210588630373</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.145098649259019</v>
+        <v>1.510249431276693</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.656036544665127</v>
+        <v>3.87512701387573</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.514875089945583</v>
+        <v>-1.166574631087499</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.372677048462475</v>
+        <v>2.511997232005709</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.159978995286739</v>
+        <v>1.525129777304412</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.6749709059265</v>
+        <v>3.894061375137103</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784104</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.650828098001899</v>
+        <v>-1.302527639143815</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.502398977384909</v>
+        <v>2.641719160928143</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.159978995286739</v>
+        <v>1.525129777304412</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.859074038071459</v>
+        <v>4.078164507282064</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.673236215806772</v>
+        <v>-1.324935756948687</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.485552425165953</v>
+        <v>2.624872608709187</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.159978995286739</v>
+        <v>1.525129777304412</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.851190732974453</v>
+        <v>4.070281202185057</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.821241983286171</v>
+        <v>-1.472941524428086</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.428404117723831</v>
+        <v>2.567724301267065</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.073251986423197</v>
+        <v>1.43840276844087</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.801208527205965</v>
+        <v>4.020298996416569</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.830682909174701</v>
+        <v>-1.482382450316616</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.480881465090266</v>
+        <v>2.6202016486335</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.195679103966588</v>
+        <v>1.560829885984262</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.930918515453847</v>
+        <v>4.150008984664451</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.829396145635144</v>
+        <v>-1.481095686777059</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.48428726505139</v>
+        <v>2.623607448594623</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.196965867506145</v>
+        <v>1.562116649523818</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.934581668122882</v>
+        <v>4.153672137333485</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.830953199624435</v>
+        <v>-1.482652740766351</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.481776256349448</v>
+        <v>2.621096439892682</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.196965867506145</v>
+        <v>1.562116649523818</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.932693481016657</v>
+        <v>4.15178395022726</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.8382250851479</v>
+        <v>-1.489924626289816</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.473687731742925</v>
+        <v>2.613007915286159</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.18969398198268</v>
+        <v>1.554844764000353</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.923150579305441</v>
+        <v>4.142241048516045</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.836384066089649</v>
+        <v>-1.488083607231564</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.472858149576378</v>
+        <v>2.612178333119612</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.190962208654148</v>
+        <v>1.556112990671822</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.922345525518474</v>
+        <v>4.141435994729077</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.843292771589329</v>
+        <v>-1.494992312731245</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.483168074242424</v>
+        <v>2.622488257785658</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.190962208654148</v>
+        <v>1.556112990671822</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.935418932384392</v>
+        <v>4.154509401594996</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.844854414404189</v>
+        <v>-1.496553955546104</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.48254341711648</v>
+        <v>2.621863600659714</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.190962208654148</v>
+        <v>1.556112990671822</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.935418932384392</v>
+        <v>4.154509401594996</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.872755201513662</v>
+        <v>-1.524454742655577</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.469907143399693</v>
+        <v>2.609227326942927</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.156365284511214</v>
+        <v>1.521516066528887</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913184819025633</v>
+        <v>4.132275288236237</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.875788199026336</v>
+        <v>-1.527487740168251</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.465458388371822</v>
+        <v>2.604778571915056</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.15333228699854</v>
+        <v>1.518483069016213</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.908129464495228</v>
+        <v>4.127219933705832</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.895849520302843</v>
+        <v>-1.547549061444758</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.524139819451723</v>
+        <v>2.663460002994957</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.133270965722033</v>
+        <v>1.498421747739706</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.962798631319828</v>
+        <v>4.181889100530431</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.152570338297667</v>
+        <v>-1.804269879439582</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.561763211255641</v>
+        <v>2.701083394798874</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.024856391578218</v>
+        <v>1.390007173595891</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.038061605835385</v>
+        <v>4.257152075045989</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.306556756073807</v>
+        <v>-1.958256297215723</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.569148913290824</v>
+        <v>2.708469096834058</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.024856391578218</v>
+        <v>1.390007173595891</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.107041874981025</v>
+        <v>4.326132344191629</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.256034852246141</v>
+        <v>-1.907734393388057</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.575408876942011</v>
+        <v>2.714729060485245</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.024856391578218</v>
+        <v>1.390007173595891</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.093093077101146</v>
+        <v>4.312183546311751</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.508510006253866</v>
+        <v>-2.160209547395782</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.486289304394336</v>
+        <v>2.625609487937569</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.024856391578218</v>
+        <v>1.390007173595891</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.10496356615656</v>
+        <v>4.324054035367165</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.777982808175574</v>
+        <v>-2.42968234931749</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.379710718144596</v>
+        <v>2.51903090168783</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.024856391578218</v>
+        <v>1.390007173595891</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.106174100675504</v>
+        <v>4.325264569886108</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.935526879905015</v>
+        <v>-2.587226421046931</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.320814831680141</v>
+        <v>2.460135015223375</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9579545864379435</v>
+        <v>1.323105368455617</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.070154759818661</v>
+        <v>4.289245229029264</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.064377430607061</v>
+        <v>-2.716076971748977</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.264352464135512</v>
+        <v>2.403672647678746</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.916961177587222</v>
+        <v>1.282111959604895</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.040636567244417</v>
+        <v>4.259727036455021</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215466</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.181345123245952</v>
+        <v>-2.833044664387868</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.379769443779</v>
+        <v>2.519089627322233</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.916961177587222</v>
+        <v>1.282111959604895</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.202840623943461</v>
+        <v>4.421931093154066</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.758957890400163</v>
+        <v>3.931898700584546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.656805233478649</v>
+        <v>3.920837872358462</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.181345123245952</v>
+        <v>-2.833044664387868</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.379769443779</v>
+        <v>2.519089627322233</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.916961177587222</v>
+        <v>1.282111959604895</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.649869030465017</v>
+        <v>3.913901669344829</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.3%</t>
+          <t>121.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-64.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.0%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-444.9%</t>
+          <t>-456.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-124.3%</t>
+          <t>-128.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.1%</t>
+          <t>-127.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.8%</t>
+          <t>-101.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.105346017169412</v>
+        <v>-3.254454938666582</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.188424418672508</v>
+        <v>1.12878085007364</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5275347021225815</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.747440071127569</v>
+        <v>2.692481024541323</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.0988350505551</v>
+        <v>-3.247943972052269</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.188628766872549</v>
+        <v>1.128985198273682</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5275347021225815</v>
+        <v>0.4359362911455038</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.745040032681886</v>
+        <v>2.690080986095639</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.079796922847803</v>
+        <v>-3.228905844344972</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.192768737163713</v>
+        <v>1.133125168564846</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4693510907913869</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.706654585091414</v>
+        <v>2.651695538505167</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.110923553998421</v>
+        <v>-3.26003247549559</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.357899953642147</v>
+        <v>1.298256385043279</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4693510907913869</v>
+        <v>0.3777526798143092</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.884236454030094</v>
+        <v>2.829277407443848</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.124790315332338</v>
+        <v>-3.273899236829507</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.353186578094713</v>
+        <v>1.293543009495846</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.431493174057564</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.862355032975934</v>
+        <v>2.807395986389688</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.079986143792408</v>
+        <v>-3.229095065289577</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.377116777107611</v>
+        <v>1.317473208508743</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.431493174057564</v>
+        <v>0.3398947630804863</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.86836356337286</v>
+        <v>2.813404516786614</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.932243173557406</v>
+        <v>-3.081352095054575</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.334164186478812</v>
+        <v>1.274520617879944</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5993005312924471</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.86699819899099</v>
+        <v>2.812039152404743</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.034257856088627</v>
+        <v>-3.183366777585796</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.296151934997804</v>
+        <v>1.236508366398936</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5993005312924471</v>
+        <v>0.5077021203153694</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.869791820522471</v>
+        <v>2.814832773936224</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.028105150035842</v>
+        <v>-3.177214071533012</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.299275365810576</v>
+        <v>1.239631797211709</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6054532373452314</v>
+        <v>0.5138548263681537</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8741457925458</v>
+        <v>2.819186745959553</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.044914448186344</v>
+        <v>-3.194023369683513</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.291632123290486</v>
+        <v>1.231988554691618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5886439391947298</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.863140690395609</v>
+        <v>2.808181643809362</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-2.982616449410222</v>
+        <v>-3.131725370907391</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.382886876597756</v>
+        <v>1.323243307998888</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5886439391947298</v>
+        <v>0.497045528217652</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.92947624419243</v>
+        <v>2.874517197606183</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.780826251745064</v>
+        <v>-2.929935173242233</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.265894957377946</v>
+        <v>1.206251388779078</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7866621313638842</v>
+        <v>0.6950637203868064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.850579161208049</v>
+        <v>2.795620114621803</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.616013248666217</v>
+        <v>-2.765122170163386</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.40211039093166</v>
+        <v>1.342466822332792</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9514751344427311</v>
+        <v>0.8598767234656534</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.019757195377533</v>
+        <v>2.964798148791286</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.713753793291191</v>
+        <v>-2.862862714788361</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.377641909197714</v>
+        <v>1.317998340598846</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.935585856309751</v>
+        <v>0.8439874453326732</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.024851364613788</v>
+        <v>2.969892318027542</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.616539182373526</v>
+        <v>-2.72811189025515</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.415063734389452</v>
+        <v>1.370434651236802</v>
       </c>
       <c r="F1974" t="n">
-        <v>1.032800467227417</v>
+        <v>0.978738269865884</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.081716111989059</v>
+        <v>3.04927879357214</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.540117135941599</v>
+        <v>-2.651689843823223</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.444124171002151</v>
+        <v>1.399495087849501</v>
       </c>
       <c r="F1975" t="n">
-        <v>1.032800467227417</v>
+        <v>0.978738269865884</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.080207730028988</v>
+        <v>3.047770411612068</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.495744004303031</v>
+        <v>-2.607316712184654</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.461736291093015</v>
+        <v>1.417107207940365</v>
       </c>
       <c r="F1976" t="n">
-        <v>1.077173598865985</v>
+        <v>1.023111401504452</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.106694476447565</v>
+        <v>3.074257158030646</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.372909783415863</v>
+        <v>-2.484482491297487</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.505263773586472</v>
+        <v>1.460634690433822</v>
       </c>
       <c r="F1977" t="n">
-        <v>1.077173598865985</v>
+        <v>1.023111401504452</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.101088270586156</v>
+        <v>3.068650952169236</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.325254052854808</v>
+        <v>-2.436826760736431</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.530707822838699</v>
+        <v>1.486078739686049</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.124829329427041</v>
+        <v>1.070767132065508</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.136063465950594</v>
+        <v>3.103626147533674</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.224735894356053</v>
+        <v>-2.336308602237676</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.575807459612925</v>
+        <v>1.531178376460276</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.225347487925796</v>
+        <v>1.171285290564263</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.201266734424571</v>
+        <v>3.168829416007652</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.285402484758442</v>
+        <v>-2.396975192640066</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.538295495927842</v>
+        <v>1.493666412775193</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.143649171207262</v>
+        <v>1.089586973845729</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.139002416869324</v>
+        <v>3.106565098452404</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.240564083150044</v>
+        <v>-2.352136791031668</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.56032855918183</v>
+        <v>1.515699476029181</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.148192604152131</v>
+        <v>1.094130406790598</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.145826179246874</v>
+        <v>3.113388860829954</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.341322718907043</v>
+        <v>-2.452895426788666</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.524186044510108</v>
+        <v>1.479556961357459</v>
       </c>
       <c r="F1982" t="n">
-        <v>1.059367035425126</v>
+        <v>1.005304838063593</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.096691777641749</v>
+        <v>3.064254459224829</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.297119881821142</v>
+        <v>-2.408692589702766</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.547746781872306</v>
+        <v>1.503117698719656</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.103569872511026</v>
+        <v>1.049507675149493</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.129093082421126</v>
+        <v>3.096655764004206</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.334098909484585</v>
+        <v>-2.445671617366209</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.531365171276176</v>
+        <v>1.486736088123527</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.140543774302357</v>
+        <v>1.086481576940824</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.149687423965172</v>
+        <v>3.117250105548252</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.175807491945313</v>
+        <v>-2.287380199826937</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.645929503474925</v>
+        <v>1.601300420322275</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.140543774302357</v>
+        <v>1.086481576940824</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.200935189148212</v>
+        <v>3.168497870731292</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-1.968165488310837</v>
+        <v>-2.07973819619246</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.727427009522968</v>
+        <v>1.682797926370319</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.348185777936833</v>
+        <v>1.2941235805753</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.32396109592315</v>
+        <v>3.291523777506231</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-1.917133395588309</v>
+        <v>-2.028706103469932</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.74278807485025</v>
+        <v>1.6981589916976</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.399217870659361</v>
+        <v>1.345155673297828</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.349528579794937</v>
+        <v>3.317091261378017</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-1.851909214461103</v>
+        <v>-1.963481922342727</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.786065151393837</v>
+        <v>1.741436068241187</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.464442051786567</v>
+        <v>1.410379854425034</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.405850492563966</v>
+        <v>3.373413174147046</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-1.81448219438997</v>
+        <v>-1.926054902271593</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.796996931721571</v>
+        <v>1.752367848568921</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.469693589815749</v>
+        <v>1.415631392454216</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.404962387680755</v>
+        <v>3.372525069263835</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-1.834593850424678</v>
+        <v>-1.946166558306301</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.790209061638928</v>
+        <v>1.745579978486278</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.480720934813168</v>
+        <v>1.426658737451635</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.412835587010447</v>
+        <v>3.380398268593527</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-1.780849035997473</v>
+        <v>-1.892421743879096</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.97226475843102</v>
+        <v>1.927635675278371</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.49078424425363</v>
+        <v>1.436722046892097</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.579431343695935</v>
+        <v>3.546994025279015</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-1.757057467391331</v>
+        <v>-1.868630175272954</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.101894295091294</v>
+        <v>2.057265211938645</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.514575812859772</v>
+        <v>1.460513615498239</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.713819194077437</v>
+        <v>3.681381875660517</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.730973383127523</v>
+        <v>-1.842546091009146</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.104035904810677</v>
+        <v>2.059406821658027</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.514575812859772</v>
+        <v>1.460513615498239</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.705527170091296</v>
+        <v>3.673089851674376</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.652842202278576</v>
+        <v>-1.764414910160199</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.133481572734035</v>
+        <v>2.088852489581385</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.588752623743457</v>
+        <v>1.534690426381924</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.748226452205286</v>
+        <v>3.715789133788367</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.643949740885293</v>
+        <v>-1.755522448766916</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.154592963018139</v>
+        <v>2.10996387986549</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.588752623743457</v>
+        <v>1.534690426381924</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.765780857932078</v>
+        <v>3.733343539515158</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-1.812425857855171</v>
+        <v>-1.923998565736794</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.079057563634772</v>
+        <v>2.034428480482123</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.560804788026876</v>
+        <v>1.506742590665343</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.740867203906713</v>
+        <v>3.708429885489794</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.114626328993587</v>
+        <v>-1.226199036875211</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.339447072367267</v>
+        <v>2.294817989214618</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.490456728656465</v>
+        <v>1.436394531294932</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.679928065472329</v>
+        <v>3.647490747055409</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.091905225310435</v>
+        <v>-1.203477933192058</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.339199536337433</v>
+        <v>2.294570453184783</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.490456728656465</v>
+        <v>1.436394531294932</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.670592087969233</v>
+        <v>3.638154769552314</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.090180182020391</v>
+        <v>-1.201752889902014</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.498795679504619</v>
+        <v>2.45416659635197</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.492181771946509</v>
+        <v>1.438119574584976</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.830533239794429</v>
+        <v>3.798095921377509</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.244961188798646</v>
+        <v>-1.35653389668027</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.473961099286964</v>
+        <v>2.429332016134314</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.458814097892033</v>
+        <v>1.4047519005305</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.847590457855389</v>
+        <v>3.81515313943847</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.193525855413987</v>
+        <v>-1.30509856329561</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.491210588630373</v>
+        <v>2.446581505477723</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.510249431276693</v>
+        <v>1.45618723391516</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.87512701387573</v>
+        <v>3.842689695458811</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.166574631087499</v>
+        <v>-1.278147338969122</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.511997232005709</v>
+        <v>2.46736814885306</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.525129777304412</v>
+        <v>1.471067579942879</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.894061375137103</v>
+        <v>3.861624056720184</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784104</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.302527639143815</v>
+        <v>-1.414100347025438</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.641719160928143</v>
+        <v>2.597090077775493</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.525129777304412</v>
+        <v>1.471067579942879</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.078164507282064</v>
+        <v>4.045727188865143</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.324935756948687</v>
+        <v>-1.43650846483031</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.624872608709187</v>
+        <v>2.580243525556538</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.525129777304412</v>
+        <v>1.471067579942879</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.070281202185057</v>
+        <v>4.037843883768137</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.472941524428086</v>
+        <v>-1.58451423230971</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.567724301267065</v>
+        <v>2.523095218114416</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.43840276844087</v>
+        <v>1.384340571079337</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.020298996416569</v>
+        <v>3.987861677999649</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.482382450316616</v>
+        <v>-1.593955158198239</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.6202016486335</v>
+        <v>2.575572565480851</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.560829885984262</v>
+        <v>1.506767688622729</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.150008984664451</v>
+        <v>4.117571666247531</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.481095686777059</v>
+        <v>-1.592668394658683</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.623607448594623</v>
+        <v>2.578978365441974</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.562116649523818</v>
+        <v>1.508054452162285</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.153672137333485</v>
+        <v>4.121234818916566</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.482652740766351</v>
+        <v>-1.594225448647974</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.621096439892682</v>
+        <v>2.576467356740033</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.562116649523818</v>
+        <v>1.508054452162285</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.15178395022726</v>
+        <v>4.119346631810341</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.489924626289816</v>
+        <v>-1.601497334171439</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.613007915286159</v>
+        <v>2.568378832133509</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.554844764000353</v>
+        <v>1.50078256663882</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.142241048516045</v>
+        <v>4.109803730099125</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.488083607231564</v>
+        <v>-1.599656315113188</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.612178333119612</v>
+        <v>2.567549249966962</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.556112990671822</v>
+        <v>1.502050793310289</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.141435994729077</v>
+        <v>4.108998676312158</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.494992312731245</v>
+        <v>-1.606565020612868</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.622488257785658</v>
+        <v>2.577859174633009</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.556112990671822</v>
+        <v>1.502050793310289</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.154509401594996</v>
+        <v>4.122072083178076</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.496553955546104</v>
+        <v>-1.608126663427728</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.621863600659714</v>
+        <v>2.577234517507065</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.556112990671822</v>
+        <v>1.502050793310289</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.154509401594996</v>
+        <v>4.122072083178076</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.524454742655577</v>
+        <v>-1.636027450537201</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.609227326942927</v>
+        <v>2.564598243790277</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.521516066528887</v>
+        <v>1.467453869167354</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.132275288236237</v>
+        <v>4.099837969819317</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.527487740168251</v>
+        <v>-1.639060448049875</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.604778571915056</v>
+        <v>2.560149488762407</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.518483069016213</v>
+        <v>1.46442087165468</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.127219933705832</v>
+        <v>4.094782615288912</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.547549061444758</v>
+        <v>-1.659121769326382</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.663460002994957</v>
+        <v>2.618830919842308</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.498421747739706</v>
+        <v>1.444359550378173</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.181889100530431</v>
+        <v>4.149451782113512</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.804269879439582</v>
+        <v>-1.915842587321206</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.701083394798874</v>
+        <v>2.656454311646225</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.390007173595891</v>
+        <v>1.335944976234358</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.257152075045989</v>
+        <v>4.22471475662907</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-1.958256297215723</v>
+        <v>-2.069829005097346</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.708469096834058</v>
+        <v>2.663840013681409</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.390007173595891</v>
+        <v>1.335944976234358</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.326132344191629</v>
+        <v>4.29369502577471</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-1.907734393388057</v>
+        <v>-2.01930710126968</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.714729060485245</v>
+        <v>2.670099977332596</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.390007173595891</v>
+        <v>1.335944976234358</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.312183546311751</v>
+        <v>4.27974622789483</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.160209547395782</v>
+        <v>-2.271782255277405</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.625609487937569</v>
+        <v>2.58098040478492</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.390007173595891</v>
+        <v>1.335944976234358</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.324054035367165</v>
+        <v>4.291616716950244</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.42968234931749</v>
+        <v>-2.541255057199113</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.51903090168783</v>
+        <v>2.47440181853518</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.390007173595891</v>
+        <v>1.335944976234358</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.325264569886108</v>
+        <v>4.292827251469189</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.587226421046931</v>
+        <v>-2.698799128928554</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.460135015223375</v>
+        <v>2.415505932070726</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.323105368455617</v>
+        <v>1.269043171094084</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.289245229029264</v>
+        <v>4.256807910612345</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.716076971748977</v>
+        <v>-2.8276496796306</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.403672647678746</v>
+        <v>2.359043564526097</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.282111959604895</v>
+        <v>1.228049762243362</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.259727036455021</v>
+        <v>4.227289718038102</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-2.833044664387868</v>
+        <v>-2.944617372269491</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.519089627322233</v>
+        <v>2.474460544169584</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.282111959604895</v>
+        <v>1.228049762243362</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.421931093154066</v>
+        <v>4.389493774737145</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.931898700584546</v>
+        <v>3.931898700584549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.920837872358462</v>
       </c>
       <c r="D2024" t="n">
-        <v>-2.833044664387868</v>
+        <v>-2.944617372269491</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.519089627322233</v>
+        <v>2.474460544169584</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.282111959604895</v>
+        <v>1.228049762243362</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.913901669344829</v>
+        <v>3.91390166934483</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>73.5%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>68.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.9%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-69.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.1%</t>
+          <t>-64.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-456.0%</t>
+          <t>-455.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-128.8%</t>
+          <t>-101.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.8%</t>
+          <t>-127.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.2%</t>
+          <t>-103.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.980726330216194</v>
+        <v>-7.002071832766497</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3661042677616391</v>
+        <v>0.3575660667415179</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9706175737292568</v>
+        <v>-0.99196307627956</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.57638067992431</v>
+        <v>2.563573378394128</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.831059939208679</v>
+        <v>-6.852405441758981</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4230786138516858</v>
+        <v>0.4145404128315646</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8777140824867209</v>
+        <v>-0.8990595850370241</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.629230564356873</v>
+        <v>2.61642326282669</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.698784465577792</v>
+        <v>-6.720129968128095</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4713562900510673</v>
+        <v>0.4628180890309461</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7454386088558342</v>
+        <v>-0.7667841114061374</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.703963335282431</v>
+        <v>2.691156033752249</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.54304613301805</v>
+        <v>-6.564391635568353</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5364666837626011</v>
+        <v>0.5279284827424799</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5897002762960927</v>
+        <v>-0.6110457788463959</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.800221395505913</v>
+        <v>2.787414093975731</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.294046334334469</v>
+        <v>-6.315391836884772</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6489729444596919</v>
+        <v>0.6404347434395707</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5897002762960927</v>
+        <v>-0.6110457788463959</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.813127736729572</v>
+        <v>2.80032043519939</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.399636324107574</v>
+        <v>-6.420981826657877</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4787610189512317</v>
+        <v>0.4702228179311105</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6952902660691971</v>
+        <v>-0.7166357686195002</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.621797813266491</v>
+        <v>2.608990511736309</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.418371226226171</v>
+        <v>-6.439716728776474</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5198113999808793</v>
+        <v>0.5112731989607582</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7008862757293284</v>
+        <v>-0.7222317782796315</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.666984549347498</v>
+        <v>2.654177247817316</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.270431184818571</v>
+        <v>-6.291776687368874</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4591084938557515</v>
+        <v>0.4505702928356303</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6805653598207708</v>
+        <v>-0.7019108623710739</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.559298176204465</v>
+        <v>2.546490874674283</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.217461662564583</v>
+        <v>-6.238807165114886</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4715823165038686</v>
+        <v>0.4630441154837475</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6275958375667819</v>
+        <v>-0.648941340117085</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.58236590330338</v>
+        <v>2.569558601773198</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.173913255793892</v>
+        <v>-6.195258758344195</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4820410671170516</v>
+        <v>0.4735028660969305</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6275958375667819</v>
+        <v>-0.648941340117085</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.575405291208287</v>
+        <v>2.562597989678105</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.931764862340034</v>
+        <v>-5.953110364890337</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.593362778879738</v>
+        <v>0.5848245778596168</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6275958375667819</v>
+        <v>-0.648941340117085</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.58986764558943</v>
+        <v>2.577060344059248</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.823505725217513</v>
+        <v>-5.844851227767816</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6311985541879417</v>
+        <v>0.6226603531678205</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6275958375667819</v>
+        <v>-0.648941340117085</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.584399766048625</v>
+        <v>2.571592464518443</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.700214590400382</v>
+        <v>-5.721560092950685</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6780131021253708</v>
+        <v>0.6694749011052497</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5043047027496514</v>
+        <v>-0.5256502052999545</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.65587254094948</v>
+        <v>2.643065239419299</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.679065391496938</v>
+        <v>-5.700410894047241</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6941737599240736</v>
+        <v>0.6856355589039524</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4831555038462081</v>
+        <v>-0.5045010063965112</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.676263038528871</v>
+        <v>2.66345573699869</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.435299949513494</v>
+        <v>-5.456645452063797</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7874606450645016</v>
+        <v>0.7789224440443805</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4831555038462081</v>
+        <v>-0.5045010063965112</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.672043746875922</v>
+        <v>2.65923644534574</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.333537129236199</v>
+        <v>-5.354882631786502</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8302900870954359</v>
+        <v>0.8217518860753148</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4699364354537794</v>
+        <v>-0.4912819380040825</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.682099501831396</v>
+        <v>2.669292200301213</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.083686735287125</v>
+        <v>-5.105032237837428</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9229723196587676</v>
+        <v>0.9144341186386464</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4699364354537794</v>
+        <v>-0.4912819380040825</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.674841576815098</v>
+        <v>2.662034275284916</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.907794642819692</v>
+        <v>-4.929140145369995</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9969282801663897</v>
+        <v>0.9883900791462681</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4699364354537794</v>
+        <v>-0.4912819380040825</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.678440700335746</v>
+        <v>2.665633398805564</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.736348179797228</v>
+        <v>-4.757693682347532</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.078834371429929</v>
+        <v>1.070296170409807</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2984899724313163</v>
+        <v>-0.3198354749816193</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.794636084203778</v>
+        <v>2.781828782673596</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.662058614058889</v>
+        <v>-4.683404116609193</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.107570675341561</v>
+        <v>1.09903247432144</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.224200406692977</v>
+        <v>-0.2455459092432801</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.838230301263078</v>
+        <v>2.825422999732897</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.598422871824955</v>
+        <v>-4.619768374375258</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.137719773289452</v>
+        <v>1.129181572269331</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1605646644590424</v>
+        <v>-0.1819101670093455</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.881106547657756</v>
+        <v>2.868299246127575</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.486996112499035</v>
+        <v>-4.508341615049338</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.163484735803616</v>
+        <v>1.154946534783495</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1605646644590424</v>
+        <v>-0.1819101670093455</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.862300806441552</v>
+        <v>2.84949350491137</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.246565615694174</v>
+        <v>-4.267911118244478</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.261400011150438</v>
+        <v>1.252861810130316</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.07986583234581784</v>
+        <v>0.05852032979551475</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.008302181149346</v>
+        <v>2.995494879619164</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.17432304752298</v>
+        <v>-4.195668550073283</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.294226352253736</v>
+        <v>1.285688151233614</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.07986583234581784</v>
+        <v>0.05852032979551475</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.012231494984166</v>
+        <v>2.999424193453984</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.121324725241592</v>
+        <v>-4.142670227791895</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.316104265083631</v>
+        <v>1.307566064063509</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1352020913477567</v>
+        <v>0.1138565887974536</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.046111834302669</v>
+        <v>3.033304532772487</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.012519839761865</v>
+        <v>-4.033865342312168</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.356624290495515</v>
+        <v>1.348086089475394</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1352020913477567</v>
+        <v>0.1138565887974536</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.043109905522662</v>
+        <v>3.030302603992481</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.792499041724854</v>
+        <v>-3.813844544275157</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.446211646720934</v>
+        <v>1.437673445700812</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2764219364157369</v>
+        <v>0.2550764338654338</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.129420849574065</v>
+        <v>3.116613548043883</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.659631352661576</v>
+        <v>-3.680976855211879</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.515252905148068</v>
+        <v>1.506714704127947</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2764219364157369</v>
+        <v>0.2550764338654338</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.145315032375888</v>
+        <v>3.132507730845706</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.539458269297077</v>
+        <v>-3.560803771847381</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.56446798293417</v>
+        <v>1.555929781914048</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3965950197802359</v>
+        <v>0.3752495172299328</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.218564726834889</v>
+        <v>3.205757425304708</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.394786124197339</v>
+        <v>-3.416131626747643</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.632424943535504</v>
+        <v>1.623886742515383</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5412671648799733</v>
+        <v>0.5199216623296702</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.315456116456172</v>
+        <v>3.30264881492599</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.454660951555032</v>
+        <v>-3.476006454105335</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.594512503993853</v>
+        <v>1.585974302973732</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4813923375222812</v>
+        <v>0.4600468349719781</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.265568711442982</v>
+        <v>3.2527614099128</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.334840720644194</v>
+        <v>-3.356186223194498</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.657729765592397</v>
+        <v>1.649191564572275</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4813923375222812</v>
+        <v>0.4600468349719781</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.280857880677191</v>
+        <v>3.268050579147009</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.337310427106</v>
+        <v>-3.358655929656304</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.564386082330116</v>
+        <v>1.555847881309995</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.478922631060475</v>
+        <v>0.4575771285101719</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.187020256122548</v>
+        <v>3.174212954592367</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.40568061343001</v>
+        <v>-3.427026115980314</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.456299869285814</v>
+        <v>1.447761668265692</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4881983300966899</v>
+        <v>0.4668528275463869</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.111847537029579</v>
+        <v>3.099040235499397</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.419468666277057</v>
+        <v>-3.440814168827361</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.441221356778886</v>
+        <v>1.432683155758764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4881983300966899</v>
+        <v>0.4668528275463869</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.10228424566147</v>
+        <v>3.089476944131289</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.450461825605762</v>
+        <v>-3.471807328156066</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.253533658087791</v>
+        <v>1.244995457067669</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4881983300966899</v>
+        <v>0.4668528275463869</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.926993810701857</v>
+        <v>2.914186509171675</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.274987565813293</v>
+        <v>-3.296333068363597</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.328290593996566</v>
+        <v>1.319752392976445</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4881983300966899</v>
+        <v>0.4668528275463869</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.931561042693645</v>
+        <v>2.918753741163463</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.385923818454541</v>
+        <v>-3.407269321004845</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.259658121701274</v>
+        <v>1.251119920681152</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4881983300966899</v>
+        <v>0.4668528275463869</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.907303071454852</v>
+        <v>2.89449576992467</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.35226027298226</v>
+        <v>-3.373605775532563</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.201661853291636</v>
+        <v>1.193123652271515</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5005163730186687</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.856039512139671</v>
+        <v>2.843232210609489</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.292407653778537</v>
+        <v>-3.31375315632884</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.235775287405258</v>
+        <v>1.227237086385137</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5005163730186687</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.866211898571803</v>
+        <v>2.853404597041621</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.206164190752159</v>
+        <v>-3.227509693302463</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.265218943189669</v>
+        <v>1.256680742169548</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5218618755689718</v>
+        <v>0.5005163730186687</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.861158169145663</v>
+        <v>2.848350867615482</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.251471010151139</v>
+        <v>-3.272816512701443</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.238871990874603</v>
+        <v>1.230333789854481</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.481051712559741</v>
+        <v>0.4597062100094379</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.828447846784651</v>
+        <v>2.815640545254469</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.280504114853441</v>
+        <v>-3.301849617403744</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.227810622026784</v>
+        <v>1.219272421006662</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.481051712559741</v>
+        <v>0.4597062100094379</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.828999719817752</v>
+        <v>2.81619241828757</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.187693633402581</v>
+        <v>-3.209039135952885</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.194207506498493</v>
+        <v>1.185669305478372</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5738621940106003</v>
+        <v>0.5525166914602972</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.813958700579633</v>
+        <v>2.801151399049452</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.232083102732009</v>
+        <v>-3.253428605282313</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.178325194691323</v>
+        <v>1.169786993671202</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5294727246811727</v>
+        <v>0.5081272221308696</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.789198494906578</v>
+        <v>2.776391193376396</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.119411884495759</v>
+        <v>-3.140757387046063</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.218469390497546</v>
+        <v>1.209931189477425</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.6207984403671198</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.851876934360051</v>
+        <v>2.839069632829869</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.007034883313086</v>
+        <v>-3.02838038586339</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.268911486801282</v>
+        <v>1.260373285781161</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6421439429174229</v>
+        <v>0.6207984403671198</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.857368230190718</v>
+        <v>2.844560928660536</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.034815281214439</v>
+        <v>-3.056160783764743</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.26929652940928</v>
+        <v>1.260758328389159</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6143635450160698</v>
+        <v>0.5930180424657667</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.852197193218445</v>
+        <v>2.839389891688263</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.117816562239718</v>
+        <v>-3.139162064790022</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.074451736999822</v>
+        <v>1.0659135359797</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.574447157938593</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.679410382502794</v>
+        <v>2.666603080972612</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.226430640683049</v>
+        <v>-3.247776143233353</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.151155766341695</v>
+        <v>1.142617565321574</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.574447157938593</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.799560043222</v>
+        <v>2.786752741691818</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.191021602434907</v>
+        <v>-3.21236710498521</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.179832407743275</v>
+        <v>1.171294206723154</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5957926604888961</v>
+        <v>0.574447157938593</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.814073069324323</v>
+        <v>2.801265767794141</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.152637939876755</v>
+        <v>-3.173983442427059</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.192605314108904</v>
+        <v>1.184067113088783</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.6128308204967442</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834522708201582</v>
+        <v>2.8217154066714</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.975521609841589</v>
+        <v>-2.996867112391893</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.260180874968273</v>
+        <v>1.251642673948151</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6341763230470473</v>
+        <v>0.6128308204967442</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831251737046884</v>
+        <v>2.818444435516702</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.020613854675135</v>
+        <v>-3.041959357225439</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.242827368796767</v>
+        <v>1.234289167776646</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5722802798776575</v>
+        <v>0.5509347773273544</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794797502907163</v>
+        <v>2.781990201376982</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.841238433436367</v>
+        <v>-2.862583935986671</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.308364512598689</v>
+        <v>1.299826311578567</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7290570380483762</v>
+        <v>0.7077115354980731</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.882650533116009</v>
+        <v>2.869843231585827</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.886252646956974</v>
+        <v>-2.907598149507277</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.271166282522036</v>
+        <v>1.262628081501915</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6987081427337716</v>
+        <v>0.6773626401834685</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845248651258836</v>
+        <v>2.832441349728654</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.153257157229409</v>
+        <v>-3.174602659779713</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.170056040752008</v>
+        <v>1.161517839731886</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5043451046908229</v>
+        <v>0.4829996021405199</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734322390772013</v>
+        <v>2.721515089241831</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.254454938666582</v>
+        <v>-3.275800441216886</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.12878085007364</v>
+        <v>1.120242649053518</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.4145907885952007</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692481024541323</v>
+        <v>2.67967372301114</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.247943972052269</v>
+        <v>-3.269289474602573</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.128985198273682</v>
+        <v>1.12044699725356</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4359362911455038</v>
+        <v>0.4145907885952007</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.690080986095639</v>
+        <v>2.677273684565457</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.228905844344972</v>
+        <v>-3.250251346895276</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.133125168564846</v>
+        <v>1.124586967544724</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.3564071772640062</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651695538505167</v>
+        <v>2.638888236974986</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.26003247549559</v>
+        <v>-3.281377978045894</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.298256385043279</v>
+        <v>1.289718184023158</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3777526798143092</v>
+        <v>0.3564071772640062</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.829277407443848</v>
+        <v>2.816470105913666</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.273899236829507</v>
+        <v>-3.295244739379811</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.293543009495846</v>
+        <v>1.285004808475724</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.3185492605301832</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.807395986389688</v>
+        <v>2.794588684859506</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.229095065289577</v>
+        <v>-3.250440567839881</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.317473208508743</v>
+        <v>1.308935007488622</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3398947630804863</v>
+        <v>0.3185492605301832</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.813404516786614</v>
+        <v>2.800597215256432</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.081352095054575</v>
+        <v>-3.102697597604879</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.274520617879944</v>
+        <v>1.265982416859822</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.4863566177650664</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.812039152404743</v>
+        <v>2.799231850874561</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.183366777585796</v>
+        <v>-3.2047122801361</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.236508366398936</v>
+        <v>1.227970165378815</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5077021203153694</v>
+        <v>0.4863566177650664</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814832773936224</v>
+        <v>2.802025472406042</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.177214071533012</v>
+        <v>-3.198559574083315</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.239631797211709</v>
+        <v>1.231093596191587</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5138548263681537</v>
+        <v>0.4925093238178506</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.819186745959553</v>
+        <v>2.806379444429371</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.194023369683513</v>
+        <v>-3.215368872233817</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.231988554691618</v>
+        <v>1.223450353671497</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.497045528217652</v>
+        <v>0.475700025667349</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.808181643809362</v>
+        <v>2.79537434227918</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.131725370907391</v>
+        <v>-3.153070873457695</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.323243307998888</v>
+        <v>1.314705106978766</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.497045528217652</v>
+        <v>0.475700025667349</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.874517197606183</v>
+        <v>2.861709896076001</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.929935173242233</v>
+        <v>-2.951280675792537</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.206251388779078</v>
+        <v>1.197713187758957</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6950637203868064</v>
+        <v>0.6737182178365033</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.795620114621803</v>
+        <v>2.782812813091621</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.765122170163386</v>
+        <v>-2.78646767271369</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.342466822332792</v>
+        <v>1.333928621312671</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8598767234656534</v>
+        <v>0.8385312209153503</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.964798148791286</v>
+        <v>2.951990847261104</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.862862714788361</v>
+        <v>-2.884208217338665</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.317998340598846</v>
+        <v>1.309460139578724</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8439874453326732</v>
+        <v>0.8226419427823701</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.969892318027542</v>
+        <v>2.95708501649736</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.72811189025515</v>
+        <v>-2.749457392805454</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.370434651236802</v>
+        <v>1.361896450216681</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.978738269865884</v>
+        <v>0.9573927673155809</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.04927879357214</v>
+        <v>3.036471492041958</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.651689843823223</v>
+        <v>-2.673035346373527</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.399495087849501</v>
+        <v>1.39095688682938</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.978738269865884</v>
+        <v>0.9573927673155809</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.047770411612068</v>
+        <v>3.034963110081887</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.607316712184654</v>
+        <v>-2.628662214734958</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.417107207940365</v>
+        <v>1.408569006920243</v>
       </c>
       <c r="F1976" t="n">
-        <v>1.023111401504452</v>
+        <v>1.00176589895415</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.074257158030646</v>
+        <v>3.061449856500464</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.484482491297487</v>
+        <v>-2.505827993847791</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.460634690433822</v>
+        <v>1.452096489413701</v>
       </c>
       <c r="F1977" t="n">
-        <v>1.023111401504452</v>
+        <v>1.00176589895415</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.068650952169236</v>
+        <v>3.055843650639054</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.436826760736431</v>
+        <v>-2.458172263286735</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.486078739686049</v>
+        <v>1.477540538665928</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.070767132065508</v>
+        <v>1.049421629515205</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.103626147533674</v>
+        <v>3.090818846003493</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.336308602237676</v>
+        <v>-2.35765410478798</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.531178376460276</v>
+        <v>1.522640175440155</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.171285290564263</v>
+        <v>1.14993978801396</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.168829416007652</v>
+        <v>3.15602211447747</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.396975192640066</v>
+        <v>-2.418320695190369</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.493666412775193</v>
+        <v>1.485128211755071</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.089586973845729</v>
+        <v>1.068241471295426</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.106565098452404</v>
+        <v>3.093757796922222</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.352136791031668</v>
+        <v>-2.373482293581971</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.515699476029181</v>
+        <v>1.507161275009059</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.094130406790598</v>
+        <v>1.072784904240295</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.113388860829954</v>
+        <v>3.100581559299772</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.452895426788666</v>
+        <v>-2.47424092933897</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.479556961357459</v>
+        <v>1.471018760337337</v>
       </c>
       <c r="F1982" t="n">
-        <v>1.005304838063593</v>
+        <v>0.9839593355132901</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.064254459224829</v>
+        <v>3.051447157694647</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.408692589702766</v>
+        <v>-2.430038092253069</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.503117698719656</v>
+        <v>1.494579497699535</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.049507675149493</v>
+        <v>1.028162172599191</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.096655764004206</v>
+        <v>3.083848462474025</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.445671617366209</v>
+        <v>-2.467017119916513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.486736088123527</v>
+        <v>1.478197887103405</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.086481576940824</v>
+        <v>1.065136074390521</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.117250105548252</v>
+        <v>3.10444280401807</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.287380199826937</v>
+        <v>-2.30872570237724</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.601300420322275</v>
+        <v>1.592762219302154</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.086481576940824</v>
+        <v>1.065136074390521</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.168497870731292</v>
+        <v>3.15569056920111</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.07973819619246</v>
+        <v>-2.101083698742764</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.682797926370319</v>
+        <v>1.674259725350197</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.2941235805753</v>
+        <v>1.272778078024997</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.291523777506231</v>
+        <v>3.278716475976049</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.028706103469932</v>
+        <v>-2.050051606020236</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.6981589916976</v>
+        <v>1.689620790677479</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.345155673297828</v>
+        <v>1.323810170747525</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.317091261378017</v>
+        <v>3.304283959847836</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-1.963481922342727</v>
+        <v>-1.98482742489303</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.741436068241187</v>
+        <v>1.732897867221066</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.410379854425034</v>
+        <v>1.389034351874731</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.373413174147046</v>
+        <v>3.360605872616864</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-1.926054902271593</v>
+        <v>-1.947400404821897</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.752367848568921</v>
+        <v>1.7438296475488</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.415631392454216</v>
+        <v>1.394285889903913</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.372525069263835</v>
+        <v>3.359717767733653</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-1.946166558306301</v>
+        <v>-1.967512060856605</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.745579978486278</v>
+        <v>1.737041777466157</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.426658737451635</v>
+        <v>1.405313234901332</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.380398268593527</v>
+        <v>3.367590967063345</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-1.892421743879096</v>
+        <v>-1.9137672464294</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.927635675278371</v>
+        <v>1.919097474258249</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.436722046892097</v>
+        <v>1.415376544341794</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.546994025279015</v>
+        <v>3.534186723748833</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-1.868630175272954</v>
+        <v>-1.889975677823258</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.057265211938645</v>
+        <v>2.048727010918523</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.460513615498239</v>
+        <v>1.439168112947936</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.681381875660517</v>
+        <v>3.668574574130336</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.842546091009146</v>
+        <v>-1.86389159355945</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.059406821658027</v>
+        <v>2.050868620637906</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.460513615498239</v>
+        <v>1.439168112947936</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.673089851674376</v>
+        <v>3.660282550144195</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.764414910160199</v>
+        <v>-1.785760412710503</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.088852489581385</v>
+        <v>2.080314288561264</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.534690426381924</v>
+        <v>1.513344923831621</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.715789133788367</v>
+        <v>3.702981832258185</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.755522448766916</v>
+        <v>-1.77686795131722</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.10996387986549</v>
+        <v>2.101425678845368</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.534690426381924</v>
+        <v>1.513344923831621</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.733343539515158</v>
+        <v>3.720536237984977</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-1.923998565736794</v>
+        <v>-1.945344068287098</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.034428480482123</v>
+        <v>2.025890279462002</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.506742590665343</v>
+        <v>1.48539708811504</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.708429885489794</v>
+        <v>3.695622583959612</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.226199036875211</v>
+        <v>-1.247544539425514</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.294817989214618</v>
+        <v>2.286279788194496</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.436394531294932</v>
+        <v>1.41504902874463</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.647490747055409</v>
+        <v>3.634683445525227</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.203477933192058</v>
+        <v>-1.224823435742362</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.294570453184783</v>
+        <v>2.286032252164662</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.436394531294932</v>
+        <v>1.41504902874463</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.638154769552314</v>
+        <v>3.625347468022132</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.201752889902014</v>
+        <v>-1.223098392452318</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.45416659635197</v>
+        <v>2.445628395331848</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.438119574584976</v>
+        <v>1.416774072034673</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.798095921377509</v>
+        <v>3.785288619847327</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.35653389668027</v>
+        <v>-1.377879399230574</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.429332016134314</v>
+        <v>2.420793815114193</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.4047519005305</v>
+        <v>1.383406397980197</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.81515313943847</v>
+        <v>3.802345837908288</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.30509856329561</v>
+        <v>-1.326444065845914</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.446581505477723</v>
+        <v>2.438043304457602</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.45618723391516</v>
+        <v>1.434841731364857</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.842689695458811</v>
+        <v>3.829882393928629</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.278147338969122</v>
+        <v>-1.299492841519426</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.46736814885306</v>
+        <v>2.458829947832939</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.471067579942879</v>
+        <v>1.449722077392576</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.861624056720184</v>
+        <v>3.848816755190002</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.414100347025438</v>
+        <v>-1.435445849575742</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.597090077775493</v>
+        <v>2.588551876755372</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.471067579942879</v>
+        <v>1.449722077392576</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.045727188865143</v>
+        <v>4.032919887334962</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.43650846483031</v>
+        <v>-1.457853967380614</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.580243525556538</v>
+        <v>2.571705324536416</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.471067579942879</v>
+        <v>1.449722077392576</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.037843883768137</v>
+        <v>4.025036582237955</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.58451423230971</v>
+        <v>-1.605859734860013</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.523095218114416</v>
+        <v>2.514557017094294</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.384340571079337</v>
+        <v>1.362995068529034</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.987861677999649</v>
+        <v>3.975054376469467</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.593955158198239</v>
+        <v>-1.615300660748543</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.575572565480851</v>
+        <v>2.567034364460729</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.506767688622729</v>
+        <v>1.485422186072426</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.117571666247531</v>
+        <v>4.104764364717349</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.592668394658683</v>
+        <v>-1.614013897208987</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.578978365441974</v>
+        <v>2.570440164421853</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.508054452162285</v>
+        <v>1.486708949611982</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.121234818916566</v>
+        <v>4.108427517386384</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.594225448647974</v>
+        <v>-1.615570951198278</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.576467356740033</v>
+        <v>2.567929155719912</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.508054452162285</v>
+        <v>1.486708949611982</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.119346631810341</v>
+        <v>4.106539330280159</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.601497334171439</v>
+        <v>-1.622842836721743</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.568378832133509</v>
+        <v>2.559840631113388</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.50078256663882</v>
+        <v>1.479437064088517</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.109803730099125</v>
+        <v>4.096996428568943</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.599656315113188</v>
+        <v>-1.621001817663491</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.567549249966962</v>
+        <v>2.559011048946841</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.502050793310289</v>
+        <v>1.480705290759986</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.108998676312158</v>
+        <v>4.096191374781976</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.606565020612868</v>
+        <v>-1.627910523163172</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.577859174633009</v>
+        <v>2.569320973612887</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.502050793310289</v>
+        <v>1.480705290759986</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.122072083178076</v>
+        <v>4.109264781647894</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.608126663427728</v>
+        <v>-1.629472165978032</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.577234517507065</v>
+        <v>2.568696316486943</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.502050793310289</v>
+        <v>1.480705290759986</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.122072083178076</v>
+        <v>4.109264781647894</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.636027450537201</v>
+        <v>-1.657372953087505</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.564598243790277</v>
+        <v>2.556060042770156</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.467453869167354</v>
+        <v>1.446108366617051</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.099837969819317</v>
+        <v>4.087030668289136</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.639060448049875</v>
+        <v>-1.660405950600178</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.560149488762407</v>
+        <v>2.551611287742285</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.46442087165468</v>
+        <v>1.443075369104377</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.094782615288912</v>
+        <v>4.08197531375873</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.659121769326382</v>
+        <v>-1.680467271876686</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.618830919842308</v>
+        <v>2.610292718822186</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.444359550378173</v>
+        <v>1.42301404782787</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.149451782113512</v>
+        <v>4.13664448058333</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.915842587321206</v>
+        <v>-1.937188089871509</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.656454311646225</v>
+        <v>2.647916110626103</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.335944976234358</v>
+        <v>1.314599473684055</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.22471475662907</v>
+        <v>4.211907455098888</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.069829005097346</v>
+        <v>-2.09117450764765</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.663840013681409</v>
+        <v>2.655301812661287</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.335944976234358</v>
+        <v>1.314599473684055</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.29369502577471</v>
+        <v>4.280887724244528</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.01930710126968</v>
+        <v>-2.040652603819984</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.670099977332596</v>
+        <v>2.661561776312475</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.335944976234358</v>
+        <v>1.314599473684055</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.27974622789483</v>
+        <v>4.266938926364649</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.271782255277405</v>
+        <v>-2.293127757827708</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.58098040478492</v>
+        <v>2.572442203764798</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.335944976234358</v>
+        <v>1.314599473684055</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.291616716950244</v>
+        <v>4.278809415420063</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.541255057199113</v>
+        <v>-2.562600559749416</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.47440181853518</v>
+        <v>2.465863617515059</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.335944976234358</v>
+        <v>1.314599473684055</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.292827251469189</v>
+        <v>4.280019949939007</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.698799128928554</v>
+        <v>-2.720144631478858</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.415505932070726</v>
+        <v>2.406967731050604</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.269043171094084</v>
+        <v>1.247697668543781</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.256807910612345</v>
+        <v>4.244000609082163</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.8276496796306</v>
+        <v>-2.848995182180904</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.359043564526097</v>
+        <v>2.350505363505975</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.228049762243362</v>
+        <v>1.206704259693059</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.227289718038102</v>
+        <v>4.21448241650792</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-2.944617372269491</v>
+        <v>-2.965962874819795</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.474460544169584</v>
+        <v>2.465922343149463</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.228049762243362</v>
+        <v>1.206704259693059</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.389493774737145</v>
+        <v>4.376686473206964</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.931898700584549</v>
+        <v>3.565337141100686</v>
       </c>
       <c r="C2024" t="n">
         <v>3.920837872358462</v>
       </c>
       <c r="D2024" t="n">
-        <v>-2.944617372269491</v>
+        <v>-2.940870392563002</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.474460544169584</v>
+        <v>2.744133291019514</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.228049762243362</v>
+        <v>1.206704259693059</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.91390166934483</v>
+        <v>4.644860428174298</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240713.xlsx
+++ b/tame_output/ON/bt/strategyON_20240713.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>457.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-455.7%</t>
+          <t>-478.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-101.8%</t>
+          <t>-139.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.4%</t>
+          <t>-135.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.3%</t>
+          <t>-119.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>-20.0%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.292815460478023</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.1855692696899243</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.18186648880097</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.422793445534451</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.569214522496813</v>
+        <v>-8.440341548483666</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2932353381758679</v>
+        <v>-0.2416861485706092</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.458265550819761</v>
+        <v>-1.329392576806614</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.259847564644748</v>
+        <v>2.337171349052637</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.773472697826676</v>
+        <v>-8.644599723813529</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3694254111891708</v>
+        <v>-0.3178762215839122</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.58590449543375</v>
+        <v>-1.457031521420603</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.188777394994997</v>
+        <v>2.266101179402885</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.80712553633515</v>
+        <v>-8.678252562322003</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3784039921081241</v>
+        <v>-0.3268548025028655</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.686317863350788</v>
+        <v>-1.55744488933764</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.133011928729211</v>
+        <v>2.210335713137099</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.733655704667701</v>
+        <v>-8.604782730654554</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3336443579477235</v>
+        <v>-0.2820951683424648</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.612848031683339</v>
+        <v>-1.483975057670192</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.192465529223101</v>
+        <v>2.269789313630989</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.908780122054244</v>
+        <v>-8.779907148041097</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3891389041548239</v>
+        <v>-0.3375897145495652</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.787972449069883</v>
+        <v>-1.659099475056736</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.101946099538692</v>
+        <v>2.17926988394658</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.143232216068734</v>
+        <v>-9.014359242055587</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4901389066622159</v>
+        <v>-0.4385897170569573</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.787972449069883</v>
+        <v>-1.659099475056736</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.094726934637095</v>
+        <v>2.172050719044984</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.24760694709518</v>
+        <v>-9.118733973082033</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5385609898467707</v>
+        <v>-0.487011800241512</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.892347180096329</v>
+        <v>-1.763474206083181</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.025429905247252</v>
+        <v>2.10275368965514</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.300393102695507</v>
+        <v>-9.17152012868236</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5585596622483449</v>
+        <v>-0.5070104726430862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.988022666678726</v>
+        <v>-1.859149692665579</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.96914040313637</v>
+        <v>2.046464187544258</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.426429896063796</v>
+        <v>-9.297556922050649</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6062806509665459</v>
+        <v>-0.5547314613612873</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.962771043868984</v>
+        <v>-1.833898069855836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.98698510545133</v>
+        <v>2.064308889859218</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.369358124167865</v>
+        <v>-9.240485150154718</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.579461606521773</v>
+        <v>-0.5279124169165144</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.962771043868984</v>
+        <v>-1.833898069855836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.990975441137731</v>
+        <v>2.068299225545619</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.511029965891986</v>
+        <v>-9.382156991878839</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6376055701101628</v>
+        <v>-0.5860563805049042</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.962771043868984</v>
+        <v>-1.833898069855836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.989500214238989</v>
+        <v>2.066823998646877</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.461439121467151</v>
+        <v>-9.332566147454004</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6027158221753566</v>
+        <v>-0.5511666325700979</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.91318019944415</v>
+        <v>-1.784307225431002</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.034308131058761</v>
+        <v>2.11163191546665</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.312520786995295</v>
+        <v>-9.183647812982148</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5561996220332972</v>
+        <v>-0.5046504324280385</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.881930608708977</v>
+        <v>-1.753057634695829</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.040006751853182</v>
+        <v>2.117330536261071</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.086675634275885</v>
+        <v>-8.957802660262736</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4562824879093244</v>
+        <v>-0.4047332983040648</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.840003933121813</v>
+        <v>-1.711130959108666</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.074741830241689</v>
+        <v>2.152065614649578</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.962096977938293</v>
+        <v>-8.833224003925144</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4053118808182288</v>
+        <v>-0.3537626912129692</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.840003933121813</v>
+        <v>-1.711130959108666</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.075880974797748</v>
+        <v>2.153204759205637</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.014992265982579</v>
+        <v>-8.886119291969431</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4238362218738359</v>
+        <v>-0.3722870322685763</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.835048587033367</v>
+        <v>-1.706175613020219</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.081487956612924</v>
+        <v>2.158811741020812</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.942859090694698</v>
+        <v>-8.81398611668155</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3892492475200466</v>
+        <v>-0.3377000579147875</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.835048587033367</v>
+        <v>-1.706175613020219</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.08722166085156</v>
+        <v>2.164545445259448</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.871492698085051</v>
+        <v>-8.742619724071902</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3704399528700533</v>
+        <v>-0.3188907632647937</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.763682194423719</v>
+        <v>-1.634809220410572</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.120304234023484</v>
+        <v>2.197628018431372</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.778033664099826</v>
+        <v>-8.649160690086678</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.342939820588871</v>
+        <v>-0.2913906309836114</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.763682194423719</v>
+        <v>-1.634809220410572</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.110420752710576</v>
+        <v>2.187744537118465</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.510791863231429</v>
+        <v>-8.38191888921828</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2378776607408857</v>
+        <v>-0.1863284711356261</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.763682194423719</v>
+        <v>-1.634809220410572</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.108586192211202</v>
+        <v>2.185909976619091</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.412884824554938</v>
+        <v>-8.284011850541789</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.19901516024375</v>
+        <v>-0.1474659706384904</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.695696444563163</v>
+        <v>-1.566823470550015</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.149077327154076</v>
+        <v>2.226401111561964</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.38893128357898</v>
+        <v>-8.260058309565832</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1887652377078735</v>
+        <v>-0.1372160481026139</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.671742903587205</v>
+        <v>-1.542869929574058</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.164117957885144</v>
+        <v>2.241441742293032</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.124871345256183</v>
+        <v>-7.995998371243036</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09640157854050679</v>
+        <v>-0.04485238893524768</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.407682965264409</v>
+        <v>-1.278809991251261</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.309293604717069</v>
+        <v>2.386617389124957</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.417791721751345</v>
+        <v>-7.288918747738197</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1836432372011276</v>
+        <v>0.2351924268063867</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.407682965264409</v>
+        <v>-1.278809991251261</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.306506571056768</v>
+        <v>2.383830355464656</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.377607423385155</v>
+        <v>-7.248734449372007</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2000605804354452</v>
+        <v>0.2516097700407043</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.367498666898218</v>
+        <v>-1.238625692885071</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.330960773964324</v>
+        <v>2.408284558372213</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.214207552445792</v>
+        <v>-7.085334578432644</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2647873500319471</v>
+        <v>0.3163365396372062</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.204098795958855</v>
+        <v>-1.075225821945708</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.428367517748699</v>
+        <v>2.505691302156587</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.002071832766497</v>
+        <v>-6.851853356203046</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3575660667415179</v>
+        <v>0.4176534573668982</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.99196307627956</v>
+        <v>-0.8417445997161095</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.563573378394128</v>
+        <v>2.653704464332198</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.852405441758981</v>
+        <v>-6.702186965195531</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4145404128315646</v>
+        <v>0.4746278034569449</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8990595850370241</v>
+        <v>-0.7488411084735735</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.61642326282669</v>
+        <v>2.706554348764761</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.720129968128095</v>
+        <v>-6.569911491564644</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4628180890309461</v>
+        <v>0.5229054796563264</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7667841114061374</v>
+        <v>-0.6165656348426869</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.691156033752249</v>
+        <v>2.78128711969032</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.564391635568353</v>
+        <v>-6.414173159004902</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5279284827424799</v>
+        <v>0.5880158733678602</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6110457788463959</v>
+        <v>-0.4608273022829453</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.787414093975731</v>
+        <v>2.877545179913802</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.315391836884772</v>
+        <v>-6.165173360321321</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6404347434395707</v>
+        <v>0.700522134064951</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6110457788463959</v>
+        <v>-0.4608273022829453</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.80032043519939</v>
+        <v>2.89045152113746</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.420981826657877</v>
+        <v>-6.270763350094426</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4702228179311105</v>
+        <v>0.5303102085564908</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7166357686195002</v>
+        <v>-0.5664172920560497</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.608990511736309</v>
+        <v>2.699121597674379</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.439716728776474</v>
+        <v>-6.289498252213023</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5112731989607582</v>
+        <v>0.5713605895861384</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7222317782796315</v>
+        <v>-0.572013301716181</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.654177247817316</v>
+        <v>2.744308333755387</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.291776687368874</v>
+        <v>-6.141558210805424</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4505702928356303</v>
+        <v>0.5106576834610106</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7019108623710739</v>
+        <v>-0.5516923858076235</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.546490874674283</v>
+        <v>2.636621960612354</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.238807165114886</v>
+        <v>-6.088588688551435</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4630441154837475</v>
+        <v>0.5231315061091277</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.648941340117085</v>
+        <v>-0.4987228635536346</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.569558601773198</v>
+        <v>2.659689687711269</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.195258758344195</v>
+        <v>-6.045040281780745</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4735028660969305</v>
+        <v>0.5335902567223108</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.648941340117085</v>
+        <v>-0.4987228635536346</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.562597989678105</v>
+        <v>2.652729075616175</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.953110364890337</v>
+        <v>-5.802891888326887</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5848245778596168</v>
+        <v>0.6449119684849971</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.648941340117085</v>
+        <v>-0.4987228635536346</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.577060344059248</v>
+        <v>2.667191429997319</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.844851227767816</v>
+        <v>-5.694632751204365</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6226603531678205</v>
+        <v>0.6827477437932008</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.648941340117085</v>
+        <v>-0.4987228635536346</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.571592464518443</v>
+        <v>2.661723550456514</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.721560092950685</v>
+        <v>-5.571341616387234</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6694749011052497</v>
+        <v>0.7295622917306299</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5256502052999545</v>
+        <v>-0.3754317287365041</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.643065239419299</v>
+        <v>2.733196325357369</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.700410894047241</v>
+        <v>-5.550192417483791</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6856355589039524</v>
+        <v>0.7457229495293327</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5045010063965112</v>
+        <v>-0.3542825298330607</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.66345573699869</v>
+        <v>2.75358682293676</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.456645452063797</v>
+        <v>-5.306426975500346</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7789224440443805</v>
+        <v>0.8390098346697608</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5045010063965112</v>
+        <v>-0.3542825298330607</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.65923644534574</v>
+        <v>2.749367531283811</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.354882631786502</v>
+        <v>-5.204664155223051</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8217518860753148</v>
+        <v>0.8818392767006951</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4912819380040825</v>
+        <v>-0.341063461440632</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.669292200301213</v>
+        <v>2.759423286239284</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.105032237837428</v>
+        <v>-4.954813761273977</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9144341186386464</v>
+        <v>0.9745215092640269</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4912819380040825</v>
+        <v>-0.341063461440632</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.662034275284916</v>
+        <v>2.752165361222986</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.929140145369995</v>
+        <v>-4.778921668806545</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9883900791462681</v>
+        <v>1.048477469771648</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4912819380040825</v>
+        <v>-0.341063461440632</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.665633398805564</v>
+        <v>2.755764484743635</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.757693682347532</v>
+        <v>-4.607475205784081</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.070296170409807</v>
+        <v>1.130383561035188</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3198354749816193</v>
+        <v>-0.1696169984181689</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.781828782673596</v>
+        <v>2.871959868611666</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.683404116609193</v>
+        <v>-4.533185640045742</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.09903247432144</v>
+        <v>1.15911986494682</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2455459092432801</v>
+        <v>-0.09532743267982963</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.825422999732897</v>
+        <v>2.915554085670967</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.619768374375258</v>
+        <v>-4.469549897811808</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.129181572269331</v>
+        <v>1.189268962894711</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1819101670093455</v>
+        <v>-0.03169169044589509</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.868299246127575</v>
+        <v>2.958430332065645</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.508341615049338</v>
+        <v>-4.358123138485888</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.154946534783495</v>
+        <v>1.215033925408875</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1819101670093455</v>
+        <v>-0.03169169044589509</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.84949350491137</v>
+        <v>2.93962459084944</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.267911118244478</v>
+        <v>-4.117692641681027</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.252861810130316</v>
+        <v>1.312949200755696</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.05852032979551475</v>
+        <v>0.2087388063589652</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.995494879619164</v>
+        <v>3.085625965557234</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.195668550073283</v>
+        <v>-4.045450073509833</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.285688151233614</v>
+        <v>1.345775541858995</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.05852032979551475</v>
+        <v>0.2087388063589652</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.999424193453984</v>
+        <v>3.089555279392054</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.142670227791895</v>
+        <v>-3.992451751228444</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.307566064063509</v>
+        <v>1.36765345468889</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1138565887974536</v>
+        <v>0.264075065360904</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.033304532772487</v>
+        <v>3.123435618710558</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.033865342312168</v>
+        <v>-3.883646865748718</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.348086089475394</v>
+        <v>1.408173480100774</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1138565887974536</v>
+        <v>0.264075065360904</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.030302603992481</v>
+        <v>3.120433689930551</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.813844544275157</v>
+        <v>-3.663626067711707</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.437673445700812</v>
+        <v>1.497760836326193</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2550764338654338</v>
+        <v>0.4052949104288843</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.116613548043883</v>
+        <v>3.206744633981953</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.680976855211879</v>
+        <v>-3.530758378648429</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.506714704127947</v>
+        <v>1.566802094753327</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2550764338654338</v>
+        <v>0.4052949104288843</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.132507730845706</v>
+        <v>3.222638816783777</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.560803771847381</v>
+        <v>-3.41058529528393</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.555929781914048</v>
+        <v>1.616017172539428</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3752495172299328</v>
+        <v>0.5254679937933833</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.205757425304708</v>
+        <v>3.295888511242778</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.416131626747643</v>
+        <v>-3.265913150184192</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.623886742515383</v>
+        <v>1.683974133140763</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5199216623296702</v>
+        <v>0.6701401388931207</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.30264881492599</v>
+        <v>3.39277990086406</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.476006454105335</v>
+        <v>-3.325787977541885</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.585974302973732</v>
+        <v>1.646061693599112</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4600468349719781</v>
+        <v>0.6102653115354286</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.2527614099128</v>
+        <v>3.342892495850871</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.356186223194498</v>
+        <v>-3.205967746631047</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.649191564572275</v>
+        <v>1.709278955197655</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4600468349719781</v>
+        <v>0.6102653115354286</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268050579147009</v>
+        <v>3.358181665085079</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.358655929656304</v>
+        <v>-3.208437453092853</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.555847881309995</v>
+        <v>1.615935271935375</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4575771285101719</v>
+        <v>0.6077956050736224</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174212954592367</v>
+        <v>3.264344040530437</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.427026115980314</v>
+        <v>-3.276807639416863</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.447761668265692</v>
+        <v>1.507849058891072</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4668528275463869</v>
+        <v>0.6170713041098373</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.099040235499397</v>
+        <v>3.189171321437467</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.440814168827361</v>
+        <v>-3.29059569226391</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.432683155758764</v>
+        <v>1.492770546384145</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4668528275463869</v>
+        <v>0.6170713041098373</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.089476944131289</v>
+        <v>3.179608030069359</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.471807328156066</v>
+        <v>-3.321588851592615</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.244995457067669</v>
+        <v>1.30508284769305</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4668528275463869</v>
+        <v>0.6170713041098373</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.914186509171675</v>
+        <v>3.004317595109745</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.296333068363597</v>
+        <v>-3.146114591800146</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.319752392976445</v>
+        <v>1.379839783601825</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4668528275463869</v>
+        <v>0.6170713041098373</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.918753741163463</v>
+        <v>3.008884827101533</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.407269321004845</v>
+        <v>-3.257050844441395</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.251119920681152</v>
+        <v>1.311207311306533</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4668528275463869</v>
+        <v>0.6170713041098373</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.89449576992467</v>
+        <v>2.98462685586274</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.373605775532563</v>
+        <v>-3.223387298969113</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.193123652271515</v>
+        <v>1.253211042896895</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5005163730186687</v>
+        <v>0.6507348495821192</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.843232210609489</v>
+        <v>2.933363296547559</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.31375315632884</v>
+        <v>-3.16353467976539</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.227237086385137</v>
+        <v>1.287324477010517</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5005163730186687</v>
+        <v>0.6507348495821192</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.853404597041621</v>
+        <v>2.943535682979692</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.227509693302463</v>
+        <v>-3.077291216739012</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.256680742169548</v>
+        <v>1.316768132794928</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5005163730186687</v>
+        <v>0.6507348495821192</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.848350867615482</v>
+        <v>2.938481953553552</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.272816512701443</v>
+        <v>-3.122598036137992</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.230333789854481</v>
+        <v>1.290421180479862</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4597062100094379</v>
+        <v>0.6099246865728885</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.815640545254469</v>
+        <v>2.905771631192539</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.301849617403744</v>
+        <v>-3.151631140840294</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.219272421006662</v>
+        <v>1.279359811632043</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4597062100094379</v>
+        <v>0.6099246865728885</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.81619241828757</v>
+        <v>2.906323504225641</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.209039135952885</v>
+        <v>-3.058820659389434</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.185669305478372</v>
+        <v>1.245756696103752</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5525166914602972</v>
+        <v>0.7027351680237478</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.801151399049452</v>
+        <v>2.891282484987522</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.253428605282313</v>
+        <v>-3.103210128718862</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.169786993671202</v>
+        <v>1.229874384296582</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5081272221308696</v>
+        <v>0.6583456986943201</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.776391193376396</v>
+        <v>2.866522279314466</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.140757387046063</v>
+        <v>-2.990538910482612</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.209931189477425</v>
+        <v>1.270018580102805</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6207984403671198</v>
+        <v>0.7710169169305703</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.839069632829869</v>
+        <v>2.929200718767939</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.02838038586339</v>
+        <v>-2.878161909299939</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.260373285781161</v>
+        <v>1.320460676406541</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6207984403671198</v>
+        <v>0.7710169169305703</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.844560928660536</v>
+        <v>2.934692014598606</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.056160783764743</v>
+        <v>-2.905942307201292</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.260758328389159</v>
+        <v>1.320845719014539</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5930180424657667</v>
+        <v>0.7432365190292172</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.839389891688263</v>
+        <v>2.929520977626334</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.139162064790022</v>
+        <v>-2.988943588226571</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.0659135359797</v>
+        <v>1.126000926605081</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.574447157938593</v>
+        <v>0.7246656345020435</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.666603080972612</v>
+        <v>2.756734166910683</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.247776143233353</v>
+        <v>-3.097557666669903</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.142617565321574</v>
+        <v>1.202704955946954</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.574447157938593</v>
+        <v>0.7246656345020435</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.786752741691818</v>
+        <v>2.876883827629888</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.21236710498521</v>
+        <v>-3.06214862842176</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.171294206723154</v>
+        <v>1.231381597348534</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.574447157938593</v>
+        <v>0.7246656345020435</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.801265767794141</v>
+        <v>2.891396853732211</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.173983442427059</v>
+        <v>-3.023764965863609</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.184067113088783</v>
+        <v>1.244154503714163</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6128308204967442</v>
+        <v>0.7630492970601946</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.8217154066714</v>
+        <v>2.911846492609471</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.996867112391893</v>
+        <v>-2.846648635828442</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.251642673948151</v>
+        <v>1.311730064573531</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6128308204967442</v>
+        <v>0.7630492970601946</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.818444435516702</v>
+        <v>2.908575521454773</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.041959357225439</v>
+        <v>-2.891740880661988</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.234289167776646</v>
+        <v>1.294376558402026</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5509347773273544</v>
+        <v>0.7011532538908049</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.781990201376982</v>
+        <v>2.872121287315052</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.862583935986671</v>
+        <v>-2.71236545942322</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.299826311578567</v>
+        <v>1.359913702203948</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7077115354980731</v>
+        <v>0.8579300120615235</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.869843231585827</v>
+        <v>2.959974317523897</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.907598149507277</v>
+        <v>-2.757379672943827</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.262628081501915</v>
+        <v>1.322715472127295</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6773626401834685</v>
+        <v>0.8275811167469189</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.832441349728654</v>
+        <v>2.922572435666725</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.174602659779713</v>
+        <v>-3.024384183216262</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.161517839731886</v>
+        <v>1.221605230357266</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4829996021405199</v>
+        <v>0.6332180787039703</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.721515089241831</v>
+        <v>2.811646175179901</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.275800441216886</v>
+        <v>-3.125581964653435</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.120242649053518</v>
+        <v>1.180330039678899</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4145907885952007</v>
+        <v>0.5648092651586512</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.67967372301114</v>
+        <v>2.769804808949211</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.269289474602573</v>
+        <v>-3.119070998039122</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.12044699725356</v>
+        <v>1.18053438787894</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4145907885952007</v>
+        <v>0.5648092651586512</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.677273684565457</v>
+        <v>2.767404770503528</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.250251346895276</v>
+        <v>-3.100032870331825</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.124586967544724</v>
+        <v>1.184674358170104</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3564071772640062</v>
+        <v>0.5066256538274566</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.638888236974986</v>
+        <v>2.729019322913056</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.281377978045894</v>
+        <v>-3.131159501482443</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.289718184023158</v>
+        <v>1.349805574648538</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3564071772640062</v>
+        <v>0.5066256538274566</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816470105913666</v>
+        <v>2.906601191851736</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.295244739379811</v>
+        <v>-3.14502626281636</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.285004808475724</v>
+        <v>1.345092199101104</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3185492605301832</v>
+        <v>0.4687677370936337</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.794588684859506</v>
+        <v>2.884719770797576</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.250440567839881</v>
+        <v>-3.10022209127643</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.308935007488622</v>
+        <v>1.369022398114002</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3185492605301832</v>
+        <v>0.4687677370936337</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.800597215256432</v>
+        <v>2.890728301194502</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.102697597604879</v>
+        <v>-2.952479121041428</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.265982416859822</v>
+        <v>1.326069807485203</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4863566177650664</v>
+        <v>0.6365750943285169</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.799231850874561</v>
+        <v>2.889362936812632</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.2047122801361</v>
+        <v>-3.054493803572649</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.227970165378815</v>
+        <v>1.288057556004195</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4863566177650664</v>
+        <v>0.6365750943285169</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.802025472406042</v>
+        <v>2.892156558344113</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.198559574083315</v>
+        <v>-3.048341097519865</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.231093596191587</v>
+        <v>1.291180986816967</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4925093238178506</v>
+        <v>0.6427278003813012</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.806379444429371</v>
+        <v>2.896510530367442</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.509954326878771</v>
+        <v>2.495329887021522</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.215368872233817</v>
+        <v>-3.065150395670366</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.223450353671497</v>
+        <v>1.268913304439628</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.475700025667349</v>
+        <v>0.6259185022307996</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.79537434227918</v>
+        <v>2.870880988360002</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.576289880675592</v>
+        <v>2.561665440818343</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.153070873457695</v>
+        <v>-3.002852396894244</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.314705106978766</v>
+        <v>1.360168057746898</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.475700025667349</v>
+        <v>0.6259185022307996</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861709896076001</v>
+        <v>2.937216542156823</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.378581882389719</v>
+        <v>2.36395744253247</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.951280675792537</v>
+        <v>-2.801062199229087</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.197713187758957</v>
+        <v>1.243176138527088</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6737182178365033</v>
+        <v>0.823936694399954</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.782812813091621</v>
+        <v>2.858319459172443</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.448872114711894</v>
+        <v>2.434247674854645</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.78646767271369</v>
+        <v>-2.636249196150239</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.333928621312671</v>
+        <v>1.379391572080802</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8385312209153503</v>
+        <v>0.9887496974788008</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.951990847261104</v>
+        <v>3.027497493341926</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.463499850827938</v>
+        <v>2.448875410970689</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.884208217338665</v>
+        <v>-2.733989740775214</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.309460139578724</v>
+        <v>1.354923090346856</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8226419427823701</v>
+        <v>0.9728604193458206</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95708501649736</v>
+        <v>3.032591662578181</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.462035831652609</v>
+        <v>2.44741139179536</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.749457392805454</v>
+        <v>-2.910327500898143</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.361896450216681</v>
+        <v>1.282923967122356</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9573927673155809</v>
+        <v>0.7965226592228911</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.036471492041958</v>
+        <v>2.925324987329095</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.460527449692538</v>
+        <v>2.445903009835289</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.673035346373527</v>
+        <v>-2.833905454466216</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.39095688682938</v>
+        <v>1.311984403735055</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9573927673155809</v>
+        <v>0.7965226592228911</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.034963110081887</v>
+        <v>2.923816605369024</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.460390317127974</v>
+        <v>2.445765877270725</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.628662214734958</v>
+        <v>-2.789532322827648</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.408569006920243</v>
+        <v>1.329596523825919</v>
       </c>
       <c r="F1976" t="n">
-        <v>1.00176589895415</v>
+        <v>0.8408957908614597</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.061449856500464</v>
+        <v>2.950303351787601</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.454784111266564</v>
+        <v>2.440159671409316</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.505827993847791</v>
+        <v>-2.66669810194048</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.452096489413701</v>
+        <v>1.373124006319376</v>
       </c>
       <c r="F1977" t="n">
-        <v>1.00176589895415</v>
+        <v>0.8408957908614597</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.055843650639054</v>
+        <v>2.944697145926192</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.461165868294369</v>
+        <v>2.44654142843712</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.458172263286735</v>
+        <v>-2.619042371379424</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.477540538665928</v>
+        <v>1.398568055571603</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.049421629515205</v>
+        <v>0.8885515214225154</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.090818846003493</v>
+        <v>2.97967234129063</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.466058241669094</v>
+        <v>2.451433801811845</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.35765410478798</v>
+        <v>-2.51852421288067</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.522640175440155</v>
+        <v>1.44366769234583</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.14993978801396</v>
+        <v>0.9890696799212699</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.15602211447747</v>
+        <v>3.044875609764607</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.452812914144966</v>
+        <v>2.438188474287717</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.418320695190369</v>
+        <v>-2.579190803283059</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.485128211755071</v>
+        <v>1.406155728660747</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.068241471295426</v>
+        <v>0.9073713632027363</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.093757796922222</v>
+        <v>2.982611292209359</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.456910616755595</v>
+        <v>2.442286176898346</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.373482293581971</v>
+        <v>-2.534352401674661</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.507161275009059</v>
+        <v>1.428188791914734</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.072784904240295</v>
+        <v>0.9119147961476057</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.100581559299772</v>
+        <v>2.98943505458691</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.461071556386673</v>
+        <v>2.446447116529424</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.47424092933897</v>
+        <v>-2.635111037431659</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.471018760337337</v>
+        <v>1.392046277243013</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9839593355132901</v>
+        <v>0.8230892274206003</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.051447157694647</v>
+        <v>2.940300652981784</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.46695115891451</v>
+        <v>2.452326719057261</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.430038092253069</v>
+        <v>-2.590908200345759</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.494579497699535</v>
+        <v>1.41560701460521</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.028162172599191</v>
+        <v>0.8672920645065008</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.083848462474025</v>
+        <v>2.972701957761162</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.465361159383757</v>
+        <v>2.450736719526509</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.467017119916513</v>
+        <v>-2.627887228009202</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.478197887103405</v>
+        <v>1.399225404009081</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.065136074390521</v>
+        <v>0.9042659662978313</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.10444280401807</v>
+        <v>2.993296299305208</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.516608924566797</v>
+        <v>2.501984484709548</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.30872570237724</v>
+        <v>-2.46959581046993</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.592762219302154</v>
+        <v>1.513789736207829</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.065136074390521</v>
+        <v>0.9042659662978313</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.15569056920111</v>
+        <v>3.044544064488247</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.51504962916105</v>
+        <v>2.500425189303801</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.101083698742764</v>
+        <v>-2.261953806835454</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.674259725350197</v>
+        <v>1.595287242255873</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.272778078024997</v>
+        <v>1.111907969932307</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.278716475976049</v>
+        <v>3.167569971263186</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.50999785739932</v>
+        <v>2.495373417542071</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.050051606020236</v>
+        <v>-2.210921714112926</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.689620790677479</v>
+        <v>1.610648307583154</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.323810170747525</v>
+        <v>1.162940062654835</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.304283959847836</v>
+        <v>3.193137455134973</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.527185261492025</v>
+        <v>2.512560821634776</v>
       </c>
       <c r="D1988" t="n">
-        <v>-1.98482742489303</v>
+        <v>-2.14569753298572</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.732897867221066</v>
+        <v>1.653925384126741</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.389034351874731</v>
+        <v>1.228164243782041</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.360605872616864</v>
+        <v>3.249459367904001</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.523146233791306</v>
+        <v>2.508521793934057</v>
       </c>
       <c r="D1989" t="n">
-        <v>-1.947400404821897</v>
+        <v>-2.108270512914586</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.7438296475488</v>
+        <v>1.664857164454475</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.394285889903913</v>
+        <v>1.233415781811223</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.359717767733653</v>
+        <v>3.248571263020791</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.524403026122546</v>
+        <v>2.509778586265297</v>
       </c>
       <c r="D1990" t="n">
-        <v>-1.967512060856605</v>
+        <v>-2.128382168949294</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.737041777466157</v>
+        <v>1.658069294371832</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.405313234901332</v>
+        <v>1.244443126808642</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.367590967063345</v>
+        <v>3.256444462350482</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.684960797143757</v>
+        <v>2.670336357286508</v>
       </c>
       <c r="D1991" t="n">
-        <v>-1.9137672464294</v>
+        <v>-2.07463735452209</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.919097474258249</v>
+        <v>1.840124991163925</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.415376544341794</v>
+        <v>1.254506436249104</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.534186723748833</v>
+        <v>3.423040219035971</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.805073706361574</v>
+        <v>2.790449266504325</v>
       </c>
       <c r="D1992" t="n">
-        <v>-1.889975677823258</v>
+        <v>-2.050845785915947</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.048727010918523</v>
+        <v>1.969754527824199</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.439168112947936</v>
+        <v>1.278298004855246</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.668574574130336</v>
+        <v>3.557428069417473</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.796781682375433</v>
+        <v>2.782157242518184</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.86389159355945</v>
+        <v>-2.024761701652139</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.050868620637906</v>
+        <v>1.971896137543581</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.439168112947936</v>
+        <v>1.278298004855246</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.660282550144195</v>
+        <v>3.549136045431332</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.794974877959212</v>
+        <v>2.780350438101963</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.785760412710503</v>
+        <v>-1.946630520803193</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.080314288561264</v>
+        <v>2.001341805466939</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.513344923831621</v>
+        <v>1.352474815738931</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.702981832258185</v>
+        <v>3.591835327545322</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.812529283686004</v>
+        <v>2.797904843828755</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.77686795131722</v>
+        <v>-1.937738059409909</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.101425678845368</v>
+        <v>2.022453195751044</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.513344923831621</v>
+        <v>1.352474815738931</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.720536237984977</v>
+        <v>3.609389733272113</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.804384331090588</v>
+        <v>2.789759891233339</v>
       </c>
       <c r="D1996" t="n">
-        <v>-1.945344068287098</v>
+        <v>-2.106214176379787</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.025890279462002</v>
+        <v>1.946917796367677</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.48539708811504</v>
+        <v>1.32452698002235</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.695622583959612</v>
+        <v>3.584476079246749</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.785654028278449</v>
+        <v>2.771029588421201</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.247544539425514</v>
+        <v>-1.408414647518204</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.286279788194496</v>
+        <v>2.207307305100172</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.41504902874463</v>
+        <v>1.25417892065194</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.634683445525227</v>
+        <v>3.523536940812364</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.776318050775354</v>
+        <v>2.761693610918105</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.224823435742362</v>
+        <v>-1.385693543835051</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.286032252164662</v>
+        <v>2.207059769070337</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.41504902874463</v>
+        <v>1.25417892065194</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.625347468022132</v>
+        <v>3.514200963309269</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.935224176626523</v>
+        <v>2.920599736769274</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.223098392452318</v>
+        <v>-1.383968500545008</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.445628395331848</v>
+        <v>2.366655912237524</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.416774072034673</v>
+        <v>1.255903963941983</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.785288619847327</v>
+        <v>3.674142115134464</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>2.957677559262921</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.377879399230574</v>
+        <v>-1.538749507323263</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.420793815114193</v>
+        <v>2.341821332019868</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.383406397980197</v>
+        <v>1.222536289887507</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.802345837908288</v>
+        <v>3.691199333195425</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>2.954352915252466</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.326444065845914</v>
+        <v>-1.487314173938604</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.438043304457602</v>
+        <v>2.359070821363277</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.434841731364857</v>
+        <v>1.273971623272167</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.829882393928629</v>
+        <v>3.718735889215766</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>2.964359068897207</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.299492841519426</v>
+        <v>-1.460362949612116</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.458829947832939</v>
+        <v>2.379857464738614</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.449722077392576</v>
+        <v>1.288851969299886</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.848816755190002</v>
+        <v>3.737670250477139</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.148462201042167</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.435445849575742</v>
+        <v>-1.596315957668432</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.588551876755372</v>
+        <v>2.509579393661047</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.449722077392576</v>
+        <v>1.288851969299886</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.032919887334962</v>
+        <v>3.921773382622099</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.14057889594516</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.457853967380614</v>
+        <v>-1.618724075473304</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.571705324536416</v>
+        <v>2.492732841442092</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.449722077392576</v>
+        <v>1.288851969299886</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.025036582237955</v>
+        <v>3.913890077525092</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.142632895494798</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.605859734860013</v>
+        <v>-1.766729842952703</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.514557017094294</v>
+        <v>2.435584533999969</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.362995068529034</v>
+        <v>1.202124960436344</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.975054376469467</v>
+        <v>3.863907871756605</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.198886613216645</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.615300660748543</v>
+        <v>-1.776170768841233</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.567034364460729</v>
+        <v>2.488061881366405</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.485422186072426</v>
+        <v>1.324552077979736</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.104764364717349</v>
+        <v>3.993617860004487</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.201777707761946</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.614013897208987</v>
+        <v>-1.774884005301676</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.570440164421853</v>
+        <v>2.491467681327528</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.486708949611982</v>
+        <v>1.325838841519292</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.108427517386384</v>
+        <v>3.997281012673522</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.199889520655721</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.615570951198278</v>
+        <v>-1.776441059290967</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.567929155719912</v>
+        <v>2.488956672625587</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.486708949611982</v>
+        <v>1.325838841519292</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.106539330280159</v>
+        <v>3.995392825567297</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.194709750258583</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.622842836721743</v>
+        <v>-1.783712944814432</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.559840631113388</v>
+        <v>2.480868148019063</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.479437064088517</v>
+        <v>1.318566955995828</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.096996428568943</v>
+        <v>3.98584992385608</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.193143760468736</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.621001817663491</v>
+        <v>-1.781871925756181</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.559011048946841</v>
+        <v>2.480038565852516</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.480705290759986</v>
+        <v>1.319835182667296</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.096191374781976</v>
+        <v>3.985044870069113</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647106</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.206217167334654</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.627910523163172</v>
+        <v>-1.788780631255861</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.569320973612887</v>
+        <v>2.490348490518563</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.480705290759986</v>
+        <v>1.319835182667296</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.109264781647894</v>
+        <v>3.998118276935032</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.206217167334654</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.629472165978032</v>
+        <v>-1.790342274070721</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.568696316486943</v>
+        <v>2.489723833392619</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.480705290759986</v>
+        <v>1.319835182667296</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.109264781647894</v>
+        <v>3.998118276935032</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.204741208461656</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.657372953087505</v>
+        <v>-1.818243061180194</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.556060042770156</v>
+        <v>2.477087559675831</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.446108366617051</v>
+        <v>1.285238258524361</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.087030668289136</v>
+        <v>3.975884163576273</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.201505652438855</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.660405950600178</v>
+        <v>-1.821276058692868</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.551611287742285</v>
+        <v>2.472638804647961</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.443075369104377</v>
+        <v>1.282205261011687</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.08197531375873</v>
+        <v>3.970828809045868</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.268211612029359</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.680467271876686</v>
+        <v>-1.841337379969375</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.610292718822186</v>
+        <v>2.531320235727861</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.42301404782787</v>
+        <v>1.26214393973518</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.13664448058333</v>
+        <v>4.025497975870467</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.408523331031206</v>
       </c>
       <c r="D2016" t="n">
-        <v>-1.937188089871509</v>
+        <v>-2.098058197964199</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.647916110626103</v>
+        <v>2.568943627531779</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.314599473684055</v>
+        <v>1.153729365591365</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.211907455098888</v>
+        <v>4.100760950386025</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.477503600176846</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.09117450764765</v>
+        <v>-2.252044615740339</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.655301812661287</v>
+        <v>2.576329329566962</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.314599473684055</v>
+        <v>1.153729365591365</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.280887724244528</v>
+        <v>4.169741219531665</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.463554802296966</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.040652603819984</v>
+        <v>-2.201522711912673</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.661561776312475</v>
+        <v>2.58258929321815</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.314599473684055</v>
+        <v>1.153729365591365</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.266938926364649</v>
+        <v>4.155792421651786</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.47542529135238</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.293127757827708</v>
+        <v>-2.453997865920398</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.572442203764798</v>
+        <v>2.493469720670474</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.314599473684055</v>
+        <v>1.153729365591365</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.278809415420063</v>
+        <v>4.1676629107072</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.476635825871324</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.562600559749416</v>
+        <v>-2.723470667842106</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.465863617515059</v>
+        <v>2.386891134420734</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.314599473684055</v>
+        <v>1.153729365591365</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.280019949939007</v>
+        <v>4.168873445226144</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.480757568098646</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.720144631478858</v>
+        <v>-2.881014739571547</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.406967731050604</v>
+        <v>2.32799524795628</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.247697668543781</v>
+        <v>1.086827560451091</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.244000609082163</v>
+        <v>4.132854104369301</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.475835420834835</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.848995182180904</v>
+        <v>-3.009865290273594</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.350505363505975</v>
+        <v>2.27153288041165</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.206704259693059</v>
+        <v>1.045834151600369</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.21448241650792</v>
+        <v>4.103335911795057</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>3.638039477533879</v>
       </c>
       <c r="D2023" t="n">
-        <v>-2.965962874819795</v>
+        <v>-3.126832982912485</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.465922343149463</v>
+        <v>2.386949860055138</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.206704259693059</v>
+        <v>1.045834151600369</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.376686473206964</v>
+        <v>4.265539968494101</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.565337141100686</v>
+        <v>3.812405152309045</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.920837872358462</v>
+        <v>3.632886115497693</v>
       </c>
       <c r="D2024" t="n">
-        <v>-2.940870392563002</v>
+        <v>-3.172466704249262</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.744133291019514</v>
+        <v>2.363543009484241</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.206704259693059</v>
+        <v>1.045834151600369</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.644860428174298</v>
+        <v>4.260386606457915</v>
       </c>
     </row>
   </sheetData>
